--- a/mzzb.xlsx
+++ b/mzzb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python\mzzbscore\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CD1CE7-E15A-4772-BACF-F436AE4B13CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCFB37E-2630-4D07-A2D8-5A244F01FE26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="3195" windowWidth="29040" windowHeight="15720" tabRatio="564" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,9 +37,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
-  <si>
-    <t>2025年XX月新番X期评分（数据截止日期XXXX年XX月XX日）</t>
-  </si>
   <si>
     <t>原名</t>
   </si>
@@ -112,18 +109,23 @@
   <si>
     <t>Notes</t>
   </si>
+  <si>
+    <t>2026年XX月新番X期评分（数据截止日期XXXX年XX月XX日）</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="176" formatCode="0.000_);[Red]\(0.000\)"/>
     <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="178" formatCode="0.0_);[Red]\(0.0\)"/>
     <numFmt numFmtId="179" formatCode="0.00_ "/>
     <numFmt numFmtId="180" formatCode="0_ "/>
     <numFmt numFmtId="181" formatCode="0.000_ "/>
+    <numFmt numFmtId="182" formatCode="0.0_ "/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -365,7 +367,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -395,9 +397,6 @@
     <xf numFmtId="177" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -414,9 +413,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="12" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -449,9 +445,6 @@
     <xf numFmtId="180" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="179" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -459,9 +452,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -488,9 +478,6 @@
     <xf numFmtId="181" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -500,20 +487,11 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -536,10 +514,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -549,20 +523,81 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="12" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="4" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="10" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -571,15 +606,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFFFF8E8"/>
-      <color rgb="FFE8F8F0"/>
-      <color rgb="FFF0F0F0"/>
-      <color rgb="FFE8E8F8"/>
-      <color rgb="FFF8F8E8"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -853,1138 +879,1141 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="34.77734375" style="9" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="63" customWidth="1"/>
     <col min="4" max="4" width="10.77734375" style="7" customWidth="1"/>
     <col min="5" max="5" width="10.77734375" style="10" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" style="7" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" style="70" customWidth="1"/>
     <col min="7" max="7" width="10.77734375" style="10" customWidth="1"/>
     <col min="8" max="8" width="10.77734375" style="7" customWidth="1"/>
-    <col min="9" max="9" width="14" style="11" customWidth="1"/>
+    <col min="9" max="9" width="14" style="63" customWidth="1"/>
     <col min="10" max="10" width="14" style="7" customWidth="1"/>
     <col min="11" max="11" width="14.109375" style="8" customWidth="1"/>
-    <col min="12" max="23" width="14.6640625" style="8" customWidth="1"/>
+    <col min="12" max="13" width="14.6640625" style="73" customWidth="1"/>
+    <col min="14" max="15" width="14.6640625" style="8" customWidth="1"/>
+    <col min="16" max="16" width="14.6640625" style="76" customWidth="1"/>
+    <col min="17" max="23" width="14.6640625" style="8" customWidth="1"/>
     <col min="24" max="24" width="55.33203125" style="8" customWidth="1"/>
     <col min="25" max="25" width="43.109375" style="1" customWidth="1"/>
     <col min="26" max="26" width="49.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:917" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="57"/>
+      <c r="M1" s="78">
+        <v>20260410</v>
+      </c>
+    </row>
+    <row r="2" spans="1:917" s="12" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="M1" s="7">
-        <v>20250714</v>
-      </c>
-    </row>
-    <row r="2" spans="1:917" s="13" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="60" t="s">
+      <c r="B2" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="C2" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="D2" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="60" t="s">
+      <c r="E2" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="62" t="s">
+      <c r="F2" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="63" t="s">
+      <c r="G2" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="60" t="s">
+      <c r="H2" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="62" t="s">
+      <c r="I2" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="63" t="s">
+      <c r="J2" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="60" t="s">
+      <c r="K2" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="62" t="s">
+      <c r="L2" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="50" t="s">
+      <c r="M2" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="64" t="s">
+      <c r="N2" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="60" t="s">
+      <c r="O2" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="62" t="s">
+      <c r="P2" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="65" t="s">
+      <c r="Q2" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="60" t="s">
+      <c r="R2" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="60" t="s">
+      <c r="S2" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="60" t="s">
+      <c r="T2" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="60" t="s">
+      <c r="U2" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="60" t="s">
+      <c r="V2" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="60" t="s">
+      <c r="W2" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="66" t="s">
+      <c r="X2" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="67" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="12"/>
-      <c r="AB2" s="12"/>
-      <c r="AC2" s="12"/>
-      <c r="AD2" s="12"/>
-      <c r="AE2" s="12"/>
-      <c r="AF2" s="12"/>
-      <c r="AG2" s="12"/>
-      <c r="AH2" s="12"/>
-      <c r="AI2" s="12"/>
-      <c r="AJ2" s="12"/>
-      <c r="AK2" s="12"/>
-      <c r="AL2" s="12"/>
-      <c r="AM2" s="12"/>
-      <c r="AN2" s="12"/>
-      <c r="AO2" s="12"/>
-      <c r="AP2" s="12"/>
-      <c r="AQ2" s="12"/>
-      <c r="AR2" s="12"/>
-      <c r="AS2" s="12"/>
-      <c r="AT2" s="12"/>
-      <c r="AU2" s="12"/>
-      <c r="AV2" s="12"/>
-      <c r="AW2" s="12"/>
-      <c r="AX2" s="12"/>
-      <c r="AY2" s="12"/>
-      <c r="AZ2" s="12"/>
-      <c r="BA2" s="12"/>
-      <c r="BB2" s="12"/>
-      <c r="BC2" s="12"/>
-      <c r="BD2" s="12"/>
-      <c r="BE2" s="12"/>
-      <c r="BF2" s="12"/>
-      <c r="BG2" s="12"/>
-      <c r="BH2" s="12"/>
-      <c r="BI2" s="12"/>
-      <c r="BJ2" s="12"/>
-      <c r="BK2" s="12"/>
-      <c r="BL2" s="12"/>
-      <c r="BM2" s="12"/>
-      <c r="BN2" s="12"/>
-      <c r="BO2" s="12"/>
-      <c r="BP2" s="12"/>
-      <c r="BQ2" s="12"/>
-      <c r="BR2" s="12"/>
-      <c r="BS2" s="12"/>
-      <c r="BT2" s="12"/>
-      <c r="BU2" s="12"/>
-      <c r="BV2" s="12"/>
-      <c r="BW2" s="12"/>
-      <c r="BX2" s="12"/>
-      <c r="BY2" s="12"/>
-      <c r="BZ2" s="12"/>
-      <c r="CA2" s="12"/>
-      <c r="CB2" s="12"/>
-      <c r="CC2" s="12"/>
-      <c r="CD2" s="12"/>
-      <c r="CE2" s="12"/>
-      <c r="CF2" s="12"/>
-      <c r="CG2" s="12"/>
-      <c r="CH2" s="12"/>
-      <c r="CI2" s="12"/>
-      <c r="CJ2" s="12"/>
-      <c r="CK2" s="12"/>
-      <c r="CL2" s="12"/>
-      <c r="CM2" s="12"/>
-      <c r="CN2" s="12"/>
-      <c r="CO2" s="12"/>
-      <c r="CP2" s="12"/>
-      <c r="CQ2" s="12"/>
-      <c r="CR2" s="12"/>
-      <c r="CS2" s="12"/>
-      <c r="CT2" s="12"/>
-      <c r="CU2" s="12"/>
-      <c r="CV2" s="12"/>
-      <c r="CW2" s="12"/>
-      <c r="CX2" s="12"/>
-      <c r="CY2" s="12"/>
-      <c r="CZ2" s="12"/>
-      <c r="DA2" s="12"/>
-      <c r="DB2" s="12"/>
-      <c r="DC2" s="12"/>
-      <c r="DD2" s="12"/>
-      <c r="DE2" s="12"/>
-      <c r="DF2" s="12"/>
-      <c r="DG2" s="12"/>
-      <c r="DH2" s="12"/>
-      <c r="DI2" s="12"/>
-      <c r="DJ2" s="12"/>
-      <c r="DK2" s="12"/>
-      <c r="DL2" s="12"/>
-      <c r="DM2" s="12"/>
-      <c r="DN2" s="12"/>
-      <c r="DO2" s="12"/>
-      <c r="DP2" s="12"/>
-      <c r="DQ2" s="12"/>
-      <c r="DR2" s="12"/>
-      <c r="DS2" s="12"/>
-      <c r="DT2" s="12"/>
-      <c r="DU2" s="12"/>
-      <c r="DV2" s="12"/>
-      <c r="DW2" s="12"/>
-      <c r="DX2" s="12"/>
-      <c r="DY2" s="12"/>
-      <c r="DZ2" s="12"/>
-      <c r="EA2" s="12"/>
-      <c r="EB2" s="12"/>
-      <c r="EC2" s="12"/>
-      <c r="ED2" s="12"/>
-      <c r="EE2" s="12"/>
-      <c r="EF2" s="12"/>
-      <c r="EG2" s="12"/>
-      <c r="EH2" s="12"/>
-      <c r="EI2" s="12"/>
-      <c r="EJ2" s="12"/>
-      <c r="EK2" s="12"/>
-      <c r="EL2" s="12"/>
-      <c r="EM2" s="12"/>
-      <c r="EN2" s="12"/>
-      <c r="EO2" s="12"/>
-      <c r="EP2" s="12"/>
-      <c r="EQ2" s="12"/>
-      <c r="ER2" s="12"/>
-      <c r="ES2" s="12"/>
-      <c r="ET2" s="12"/>
-      <c r="EU2" s="12"/>
-      <c r="EV2" s="12"/>
-      <c r="EW2" s="12"/>
-      <c r="EX2" s="12"/>
-      <c r="EY2" s="12"/>
-      <c r="EZ2" s="12"/>
-      <c r="FA2" s="12"/>
-      <c r="FB2" s="12"/>
-      <c r="FC2" s="12"/>
-      <c r="FD2" s="12"/>
-      <c r="FE2" s="12"/>
-      <c r="FF2" s="12"/>
-      <c r="FG2" s="12"/>
-      <c r="FH2" s="12"/>
-      <c r="FI2" s="12"/>
-      <c r="FJ2" s="12"/>
-      <c r="FK2" s="12"/>
-      <c r="FL2" s="12"/>
-      <c r="FM2" s="12"/>
-      <c r="FN2" s="12"/>
-      <c r="FO2" s="12"/>
-      <c r="FP2" s="12"/>
-      <c r="FQ2" s="12"/>
-      <c r="FR2" s="12"/>
-      <c r="FS2" s="12"/>
-      <c r="FT2" s="12"/>
-      <c r="FU2" s="12"/>
-      <c r="FV2" s="12"/>
-      <c r="FW2" s="12"/>
-      <c r="FX2" s="12"/>
-      <c r="FY2" s="12"/>
-      <c r="FZ2" s="12"/>
-      <c r="GA2" s="12"/>
-      <c r="GB2" s="12"/>
-      <c r="GC2" s="12"/>
-      <c r="GD2" s="12"/>
-      <c r="GE2" s="12"/>
-      <c r="GF2" s="12"/>
-      <c r="GG2" s="12"/>
-      <c r="GH2" s="12"/>
-      <c r="GI2" s="12"/>
-      <c r="GJ2" s="12"/>
-      <c r="GK2" s="12"/>
-      <c r="GL2" s="12"/>
-      <c r="GM2" s="12"/>
-      <c r="GN2" s="12"/>
-      <c r="GO2" s="12"/>
-      <c r="GP2" s="12"/>
-      <c r="GQ2" s="12"/>
-      <c r="GR2" s="12"/>
-      <c r="GS2" s="12"/>
-      <c r="GT2" s="12"/>
-      <c r="GU2" s="12"/>
-      <c r="GV2" s="12"/>
-      <c r="GW2" s="12"/>
-      <c r="GX2" s="12"/>
-      <c r="GY2" s="12"/>
-      <c r="GZ2" s="12"/>
-      <c r="HA2" s="12"/>
-      <c r="HB2" s="12"/>
-      <c r="HC2" s="12"/>
-      <c r="HD2" s="12"/>
-      <c r="HE2" s="12"/>
-      <c r="HF2" s="12"/>
-      <c r="HG2" s="12"/>
-      <c r="HH2" s="12"/>
-      <c r="HI2" s="12"/>
-      <c r="HJ2" s="12"/>
-      <c r="HK2" s="12"/>
-      <c r="HL2" s="12"/>
-      <c r="HM2" s="12"/>
-      <c r="HN2" s="12"/>
-      <c r="HO2" s="12"/>
-      <c r="HP2" s="12"/>
-      <c r="HQ2" s="12"/>
-      <c r="HR2" s="12"/>
-      <c r="HS2" s="12"/>
-      <c r="HT2" s="12"/>
-      <c r="HU2" s="12"/>
-      <c r="HV2" s="12"/>
-      <c r="HW2" s="12"/>
-      <c r="HX2" s="12"/>
-      <c r="HY2" s="12"/>
-      <c r="HZ2" s="12"/>
-      <c r="IA2" s="12"/>
-      <c r="IB2" s="12"/>
-      <c r="IC2" s="12"/>
-      <c r="ID2" s="12"/>
-      <c r="IE2" s="12"/>
-      <c r="IF2" s="12"/>
-      <c r="IG2" s="12"/>
-      <c r="IH2" s="12"/>
-      <c r="II2" s="12"/>
-      <c r="IJ2" s="12"/>
-      <c r="IK2" s="12"/>
-      <c r="IL2" s="12"/>
-      <c r="IM2" s="12"/>
-      <c r="IN2" s="12"/>
-      <c r="IO2" s="12"/>
-      <c r="IP2" s="12"/>
-      <c r="IQ2" s="12"/>
-      <c r="IR2" s="12"/>
-      <c r="IS2" s="12"/>
-      <c r="IT2" s="12"/>
-      <c r="IU2" s="12"/>
-      <c r="IV2" s="12"/>
-      <c r="IW2" s="12"/>
-      <c r="IX2" s="12"/>
-      <c r="IY2" s="12"/>
-      <c r="IZ2" s="12"/>
-      <c r="JA2" s="12"/>
-      <c r="JB2" s="12"/>
-      <c r="JC2" s="12"/>
-      <c r="JD2" s="12"/>
-      <c r="JE2" s="12"/>
-      <c r="JF2" s="12"/>
-      <c r="JG2" s="12"/>
-      <c r="JH2" s="12"/>
-      <c r="JI2" s="12"/>
-      <c r="JJ2" s="12"/>
-      <c r="JK2" s="12"/>
-      <c r="JL2" s="12"/>
-      <c r="JM2" s="12"/>
-      <c r="JN2" s="12"/>
-      <c r="JO2" s="12"/>
-      <c r="JP2" s="12"/>
-      <c r="JQ2" s="12"/>
-      <c r="JR2" s="12"/>
-      <c r="JS2" s="12"/>
-      <c r="JT2" s="12"/>
-      <c r="JU2" s="12"/>
-      <c r="JV2" s="12"/>
-      <c r="JW2" s="12"/>
-      <c r="JX2" s="12"/>
-      <c r="JY2" s="12"/>
-      <c r="JZ2" s="12"/>
-      <c r="KA2" s="12"/>
-      <c r="KB2" s="12"/>
-      <c r="KC2" s="12"/>
-      <c r="KD2" s="12"/>
-      <c r="KE2" s="12"/>
-      <c r="KF2" s="12"/>
-      <c r="KG2" s="12"/>
-      <c r="KH2" s="12"/>
-      <c r="KI2" s="12"/>
-      <c r="KJ2" s="12"/>
-      <c r="KK2" s="12"/>
-      <c r="KL2" s="12"/>
-      <c r="KM2" s="12"/>
-      <c r="KN2" s="12"/>
-      <c r="KO2" s="12"/>
-      <c r="KP2" s="12"/>
-      <c r="KQ2" s="12"/>
-      <c r="KR2" s="12"/>
-      <c r="KS2" s="12"/>
-      <c r="KT2" s="12"/>
-      <c r="KU2" s="12"/>
-      <c r="KV2" s="12"/>
-      <c r="KW2" s="12"/>
-      <c r="KX2" s="12"/>
-      <c r="KY2" s="12"/>
-      <c r="KZ2" s="12"/>
-      <c r="LA2" s="12"/>
-      <c r="LB2" s="12"/>
-      <c r="LC2" s="12"/>
-      <c r="LD2" s="12"/>
-      <c r="LE2" s="12"/>
-      <c r="LF2" s="12"/>
-      <c r="LG2" s="12"/>
-      <c r="LH2" s="12"/>
-      <c r="LI2" s="12"/>
-      <c r="LJ2" s="12"/>
-      <c r="LK2" s="12"/>
-      <c r="LL2" s="12"/>
-      <c r="LM2" s="12"/>
-      <c r="LN2" s="12"/>
-      <c r="LO2" s="12"/>
-      <c r="LP2" s="12"/>
-      <c r="LQ2" s="12"/>
-      <c r="LR2" s="12"/>
-      <c r="LS2" s="12"/>
-      <c r="LT2" s="12"/>
-      <c r="LU2" s="12"/>
-      <c r="LV2" s="12"/>
-      <c r="LW2" s="12"/>
-      <c r="LX2" s="12"/>
-      <c r="LY2" s="12"/>
-      <c r="LZ2" s="12"/>
-      <c r="MA2" s="12"/>
-      <c r="MB2" s="12"/>
-      <c r="MC2" s="12"/>
-      <c r="MD2" s="12"/>
-      <c r="ME2" s="12"/>
-      <c r="MF2" s="12"/>
-      <c r="MG2" s="12"/>
-      <c r="MH2" s="12"/>
-      <c r="MI2" s="12"/>
-      <c r="MJ2" s="12"/>
-      <c r="MK2" s="12"/>
-      <c r="ML2" s="12"/>
-      <c r="MM2" s="12"/>
-      <c r="MN2" s="12"/>
-      <c r="MO2" s="12"/>
-      <c r="MP2" s="12"/>
-      <c r="MQ2" s="12"/>
-      <c r="MR2" s="12"/>
-      <c r="MS2" s="12"/>
-      <c r="MT2" s="12"/>
-      <c r="MU2" s="12"/>
-      <c r="MV2" s="12"/>
-      <c r="MW2" s="12"/>
-      <c r="MX2" s="12"/>
-      <c r="MY2" s="12"/>
-      <c r="MZ2" s="12"/>
-      <c r="NA2" s="12"/>
-      <c r="NB2" s="12"/>
-      <c r="NC2" s="12"/>
-      <c r="ND2" s="12"/>
-      <c r="NE2" s="12"/>
-      <c r="NF2" s="12"/>
-      <c r="NG2" s="12"/>
-      <c r="NH2" s="12"/>
-      <c r="NI2" s="12"/>
-      <c r="NJ2" s="12"/>
-      <c r="NK2" s="12"/>
-      <c r="NL2" s="12"/>
-      <c r="NM2" s="12"/>
-      <c r="NN2" s="12"/>
-      <c r="NO2" s="12"/>
-      <c r="NP2" s="12"/>
-      <c r="NQ2" s="12"/>
-      <c r="NR2" s="12"/>
-      <c r="NS2" s="12"/>
-      <c r="NT2" s="12"/>
-      <c r="NU2" s="12"/>
-      <c r="NV2" s="12"/>
-      <c r="NW2" s="12"/>
-      <c r="NX2" s="12"/>
-      <c r="NY2" s="12"/>
-      <c r="NZ2" s="12"/>
-      <c r="OA2" s="12"/>
-      <c r="OB2" s="12"/>
-      <c r="OC2" s="12"/>
-      <c r="OD2" s="12"/>
-      <c r="OE2" s="12"/>
-      <c r="OF2" s="12"/>
-      <c r="OG2" s="12"/>
-      <c r="OH2" s="12"/>
-      <c r="OI2" s="12"/>
-      <c r="OJ2" s="12"/>
-      <c r="OK2" s="12"/>
-      <c r="OL2" s="12"/>
-      <c r="OM2" s="12"/>
-      <c r="ON2" s="12"/>
-      <c r="OO2" s="12"/>
-      <c r="OP2" s="12"/>
-      <c r="OQ2" s="12"/>
-      <c r="OR2" s="12"/>
-      <c r="OS2" s="12"/>
-      <c r="OT2" s="12"/>
-      <c r="OU2" s="12"/>
-      <c r="OV2" s="12"/>
-      <c r="OW2" s="12"/>
-      <c r="OX2" s="12"/>
-      <c r="OY2" s="12"/>
-      <c r="OZ2" s="12"/>
-      <c r="PA2" s="12"/>
-      <c r="PB2" s="12"/>
-      <c r="PC2" s="12"/>
-      <c r="PD2" s="12"/>
-      <c r="PE2" s="12"/>
-      <c r="PF2" s="12"/>
-      <c r="PG2" s="12"/>
-      <c r="PH2" s="12"/>
-      <c r="PI2" s="12"/>
-      <c r="PJ2" s="12"/>
-      <c r="PK2" s="12"/>
-      <c r="PL2" s="12"/>
-      <c r="PM2" s="12"/>
-      <c r="PN2" s="12"/>
-      <c r="PO2" s="12"/>
-      <c r="PP2" s="12"/>
-      <c r="PQ2" s="12"/>
-      <c r="PR2" s="12"/>
-      <c r="PS2" s="12"/>
-      <c r="PT2" s="12"/>
-      <c r="PU2" s="12"/>
-      <c r="PV2" s="12"/>
-      <c r="PW2" s="12"/>
-      <c r="PX2" s="12"/>
-      <c r="PY2" s="12"/>
-      <c r="PZ2" s="12"/>
-      <c r="QA2" s="12"/>
-      <c r="QB2" s="12"/>
-      <c r="QC2" s="12"/>
-      <c r="QD2" s="12"/>
-      <c r="QE2" s="12"/>
-      <c r="QF2" s="12"/>
-      <c r="QG2" s="12"/>
-      <c r="QH2" s="12"/>
-      <c r="QI2" s="12"/>
-      <c r="QJ2" s="12"/>
-      <c r="QK2" s="12"/>
-      <c r="QL2" s="12"/>
-      <c r="QM2" s="12"/>
-      <c r="QN2" s="12"/>
-      <c r="QO2" s="12"/>
-      <c r="QP2" s="12"/>
-      <c r="QQ2" s="12"/>
-      <c r="QR2" s="12"/>
-      <c r="QS2" s="12"/>
-      <c r="QT2" s="12"/>
-      <c r="QU2" s="12"/>
-      <c r="QV2" s="12"/>
-      <c r="QW2" s="12"/>
-      <c r="QX2" s="12"/>
-      <c r="QY2" s="12"/>
-      <c r="QZ2" s="12"/>
-      <c r="RA2" s="12"/>
-      <c r="RB2" s="12"/>
-      <c r="RC2" s="12"/>
-      <c r="RD2" s="12"/>
-      <c r="RE2" s="12"/>
-      <c r="RF2" s="12"/>
-      <c r="RG2" s="12"/>
-      <c r="RH2" s="12"/>
-      <c r="RI2" s="12"/>
-      <c r="RJ2" s="12"/>
-      <c r="RK2" s="12"/>
-      <c r="RL2" s="12"/>
-      <c r="RM2" s="12"/>
-      <c r="RN2" s="12"/>
-      <c r="RO2" s="12"/>
-      <c r="RP2" s="12"/>
-      <c r="RQ2" s="12"/>
-      <c r="RR2" s="12"/>
-      <c r="RS2" s="12"/>
-      <c r="RT2" s="12"/>
-      <c r="RU2" s="12"/>
-      <c r="RV2" s="12"/>
-      <c r="RW2" s="12"/>
-      <c r="RX2" s="12"/>
-      <c r="RY2" s="12"/>
-      <c r="RZ2" s="12"/>
-      <c r="SA2" s="12"/>
-      <c r="SB2" s="12"/>
-      <c r="SC2" s="12"/>
-      <c r="SD2" s="12"/>
-      <c r="SE2" s="12"/>
-      <c r="SF2" s="12"/>
-      <c r="SG2" s="12"/>
-      <c r="SH2" s="12"/>
-      <c r="SI2" s="12"/>
-      <c r="SJ2" s="12"/>
-      <c r="SK2" s="12"/>
-      <c r="SL2" s="12"/>
-      <c r="SM2" s="12"/>
-      <c r="SN2" s="12"/>
-      <c r="SO2" s="12"/>
-      <c r="SP2" s="12"/>
-      <c r="SQ2" s="12"/>
-      <c r="SR2" s="12"/>
-      <c r="SS2" s="12"/>
-      <c r="ST2" s="12"/>
-      <c r="SU2" s="12"/>
-      <c r="SV2" s="12"/>
-      <c r="SW2" s="12"/>
-      <c r="SX2" s="12"/>
-      <c r="SY2" s="12"/>
-      <c r="SZ2" s="12"/>
-      <c r="TA2" s="12"/>
-      <c r="TB2" s="12"/>
-      <c r="TC2" s="12"/>
-      <c r="TD2" s="12"/>
-      <c r="TE2" s="12"/>
-      <c r="TF2" s="12"/>
-      <c r="TG2" s="12"/>
-      <c r="TH2" s="12"/>
-      <c r="TI2" s="12"/>
-      <c r="TJ2" s="12"/>
-      <c r="TK2" s="12"/>
-      <c r="TL2" s="12"/>
-      <c r="TM2" s="12"/>
-      <c r="TN2" s="12"/>
-      <c r="TO2" s="12"/>
-      <c r="TP2" s="12"/>
-      <c r="TQ2" s="12"/>
-      <c r="TR2" s="12"/>
-      <c r="TS2" s="12"/>
-      <c r="TT2" s="12"/>
-      <c r="TU2" s="12"/>
-      <c r="TV2" s="12"/>
-      <c r="TW2" s="12"/>
-      <c r="TX2" s="12"/>
-      <c r="TY2" s="12"/>
-      <c r="TZ2" s="12"/>
-      <c r="UA2" s="12"/>
-      <c r="UB2" s="12"/>
-      <c r="UC2" s="12"/>
-      <c r="UD2" s="12"/>
-      <c r="UE2" s="12"/>
-      <c r="UF2" s="12"/>
-      <c r="UG2" s="12"/>
-      <c r="UH2" s="12"/>
-      <c r="UI2" s="12"/>
-      <c r="UJ2" s="12"/>
-      <c r="UK2" s="12"/>
-      <c r="UL2" s="12"/>
-      <c r="UM2" s="12"/>
-      <c r="UN2" s="12"/>
-      <c r="UO2" s="12"/>
-      <c r="UP2" s="12"/>
-      <c r="UQ2" s="12"/>
-      <c r="UR2" s="12"/>
-      <c r="US2" s="12"/>
-      <c r="UT2" s="12"/>
-      <c r="UU2" s="12"/>
-      <c r="UV2" s="12"/>
-      <c r="UW2" s="12"/>
-      <c r="UX2" s="12"/>
-      <c r="UY2" s="12"/>
-      <c r="UZ2" s="12"/>
-      <c r="VA2" s="12"/>
-      <c r="VB2" s="12"/>
-      <c r="VC2" s="12"/>
-      <c r="VD2" s="12"/>
-      <c r="VE2" s="12"/>
-      <c r="VF2" s="12"/>
-      <c r="VG2" s="12"/>
-      <c r="VH2" s="12"/>
-      <c r="VI2" s="12"/>
-      <c r="VJ2" s="12"/>
-      <c r="VK2" s="12"/>
-      <c r="VL2" s="12"/>
-      <c r="VM2" s="12"/>
-      <c r="VN2" s="12"/>
-      <c r="VO2" s="12"/>
-      <c r="VP2" s="12"/>
-      <c r="VQ2" s="12"/>
-      <c r="VR2" s="12"/>
-      <c r="VS2" s="12"/>
-      <c r="VT2" s="12"/>
-      <c r="VU2" s="12"/>
-      <c r="VV2" s="12"/>
-      <c r="VW2" s="12"/>
-      <c r="VX2" s="12"/>
-      <c r="VY2" s="12"/>
-      <c r="VZ2" s="12"/>
-      <c r="WA2" s="12"/>
-      <c r="WB2" s="12"/>
-      <c r="WC2" s="12"/>
-      <c r="WD2" s="12"/>
-      <c r="WE2" s="12"/>
-      <c r="WF2" s="12"/>
-      <c r="WG2" s="12"/>
-      <c r="WH2" s="12"/>
-      <c r="WI2" s="12"/>
-      <c r="WJ2" s="12"/>
-      <c r="WK2" s="12"/>
-      <c r="WL2" s="12"/>
-      <c r="WM2" s="12"/>
-      <c r="WN2" s="12"/>
-      <c r="WO2" s="12"/>
-      <c r="WP2" s="12"/>
-      <c r="WQ2" s="12"/>
-      <c r="WR2" s="12"/>
-      <c r="WS2" s="12"/>
-      <c r="WT2" s="12"/>
-      <c r="WU2" s="12"/>
-      <c r="WV2" s="12"/>
-      <c r="WW2" s="12"/>
-      <c r="WX2" s="12"/>
-      <c r="WY2" s="12"/>
-      <c r="WZ2" s="12"/>
-      <c r="XA2" s="12"/>
-      <c r="XB2" s="12"/>
-      <c r="XC2" s="12"/>
-      <c r="XD2" s="12"/>
-      <c r="XE2" s="12"/>
-      <c r="XF2" s="12"/>
-      <c r="XG2" s="12"/>
-      <c r="XH2" s="12"/>
-      <c r="XI2" s="12"/>
-      <c r="XJ2" s="12"/>
-      <c r="XK2" s="12"/>
-      <c r="XL2" s="12"/>
-      <c r="XM2" s="12"/>
-      <c r="XN2" s="12"/>
-      <c r="XO2" s="12"/>
-      <c r="XP2" s="12"/>
-      <c r="XQ2" s="12"/>
-      <c r="XR2" s="12"/>
-      <c r="XS2" s="12"/>
-      <c r="XT2" s="12"/>
-      <c r="XU2" s="12"/>
-      <c r="XV2" s="12"/>
-      <c r="XW2" s="12"/>
-      <c r="XX2" s="12"/>
-      <c r="XY2" s="12"/>
-      <c r="XZ2" s="12"/>
-      <c r="YA2" s="12"/>
-      <c r="YB2" s="12"/>
-      <c r="YC2" s="12"/>
-      <c r="YD2" s="12"/>
-      <c r="YE2" s="12"/>
-      <c r="YF2" s="12"/>
-      <c r="YG2" s="12"/>
-      <c r="YH2" s="12"/>
-      <c r="YI2" s="12"/>
-      <c r="YJ2" s="12"/>
-      <c r="YK2" s="12"/>
-      <c r="YL2" s="12"/>
-      <c r="YM2" s="12"/>
-      <c r="YN2" s="12"/>
-      <c r="YO2" s="12"/>
-      <c r="YP2" s="12"/>
-      <c r="YQ2" s="12"/>
-      <c r="YR2" s="12"/>
-      <c r="YS2" s="12"/>
-      <c r="YT2" s="12"/>
-      <c r="YU2" s="12"/>
-      <c r="YV2" s="12"/>
-      <c r="YW2" s="12"/>
-      <c r="YX2" s="12"/>
-      <c r="YY2" s="12"/>
-      <c r="YZ2" s="12"/>
-      <c r="ZA2" s="12"/>
-      <c r="ZB2" s="12"/>
-      <c r="ZC2" s="12"/>
-      <c r="ZD2" s="12"/>
-      <c r="ZE2" s="12"/>
-      <c r="ZF2" s="12"/>
-      <c r="ZG2" s="12"/>
-      <c r="ZH2" s="12"/>
-      <c r="ZI2" s="12"/>
-      <c r="ZJ2" s="12"/>
-      <c r="ZK2" s="12"/>
-      <c r="ZL2" s="12"/>
-      <c r="ZM2" s="12"/>
-      <c r="ZN2" s="12"/>
-      <c r="ZO2" s="12"/>
-      <c r="ZP2" s="12"/>
-      <c r="ZQ2" s="12"/>
-      <c r="ZR2" s="12"/>
-      <c r="ZS2" s="12"/>
-      <c r="ZT2" s="12"/>
-      <c r="ZU2" s="12"/>
-      <c r="ZV2" s="12"/>
-      <c r="ZW2" s="12"/>
-      <c r="ZX2" s="12"/>
-      <c r="ZY2" s="12"/>
-      <c r="ZZ2" s="12"/>
-      <c r="AAA2" s="12"/>
-      <c r="AAB2" s="12"/>
-      <c r="AAC2" s="12"/>
-      <c r="AAD2" s="12"/>
-      <c r="AAE2" s="12"/>
-      <c r="AAF2" s="12"/>
-      <c r="AAG2" s="12"/>
-      <c r="AAH2" s="12"/>
-      <c r="AAI2" s="12"/>
-      <c r="AAJ2" s="12"/>
-      <c r="AAK2" s="12"/>
-      <c r="AAL2" s="12"/>
-      <c r="AAM2" s="12"/>
-      <c r="AAN2" s="12"/>
-      <c r="AAO2" s="12"/>
-      <c r="AAP2" s="12"/>
-      <c r="AAQ2" s="12"/>
-      <c r="AAR2" s="12"/>
-      <c r="AAS2" s="12"/>
-      <c r="AAT2" s="12"/>
-      <c r="AAU2" s="12"/>
-      <c r="AAV2" s="12"/>
-      <c r="AAW2" s="12"/>
-      <c r="AAX2" s="12"/>
-      <c r="AAY2" s="12"/>
-      <c r="AAZ2" s="12"/>
-      <c r="ABA2" s="12"/>
-      <c r="ABB2" s="12"/>
-      <c r="ABC2" s="12"/>
-      <c r="ABD2" s="12"/>
-      <c r="ABE2" s="12"/>
-      <c r="ABF2" s="12"/>
-      <c r="ABG2" s="12"/>
-      <c r="ABH2" s="12"/>
-      <c r="ABI2" s="12"/>
-      <c r="ABJ2" s="12"/>
-      <c r="ABK2" s="12"/>
-      <c r="ABL2" s="12"/>
-      <c r="ABM2" s="12"/>
-      <c r="ABN2" s="12"/>
-      <c r="ABO2" s="12"/>
-      <c r="ABP2" s="12"/>
-      <c r="ABQ2" s="12"/>
-      <c r="ABR2" s="12"/>
-      <c r="ABS2" s="12"/>
-      <c r="ABT2" s="12"/>
-      <c r="ABU2" s="12"/>
-      <c r="ABV2" s="12"/>
-      <c r="ABW2" s="12"/>
-      <c r="ABX2" s="12"/>
-      <c r="ABY2" s="12"/>
-      <c r="ABZ2" s="12"/>
-      <c r="ACA2" s="12"/>
-      <c r="ACB2" s="12"/>
-      <c r="ACC2" s="12"/>
-      <c r="ACD2" s="12"/>
-      <c r="ACE2" s="12"/>
-      <c r="ACF2" s="12"/>
-      <c r="ACG2" s="12"/>
-      <c r="ACH2" s="12"/>
-      <c r="ACI2" s="12"/>
-      <c r="ACJ2" s="12"/>
-      <c r="ACK2" s="12"/>
-      <c r="ACL2" s="12"/>
-      <c r="ACM2" s="12"/>
-      <c r="ACN2" s="12"/>
-      <c r="ACO2" s="12"/>
-      <c r="ACP2" s="12"/>
-      <c r="ACQ2" s="12"/>
-      <c r="ACR2" s="12"/>
-      <c r="ACS2" s="12"/>
-      <c r="ACT2" s="12"/>
-      <c r="ACU2" s="12"/>
-      <c r="ACV2" s="12"/>
-      <c r="ACW2" s="12"/>
-      <c r="ACX2" s="12"/>
-      <c r="ACY2" s="12"/>
-      <c r="ACZ2" s="12"/>
-      <c r="ADA2" s="12"/>
-      <c r="ADB2" s="12"/>
-      <c r="ADC2" s="12"/>
-      <c r="ADD2" s="12"/>
-      <c r="ADE2" s="12"/>
-      <c r="ADF2" s="12"/>
-      <c r="ADG2" s="12"/>
-      <c r="ADH2" s="12"/>
-      <c r="ADI2" s="12"/>
-      <c r="ADJ2" s="12"/>
-      <c r="ADK2" s="12"/>
-      <c r="ADL2" s="12"/>
-      <c r="ADM2" s="12"/>
-      <c r="ADN2" s="12"/>
-      <c r="ADO2" s="12"/>
-      <c r="ADP2" s="12"/>
-      <c r="ADQ2" s="12"/>
-      <c r="ADR2" s="12"/>
-      <c r="ADS2" s="12"/>
-      <c r="ADT2" s="12"/>
-      <c r="ADU2" s="12"/>
-      <c r="ADV2" s="12"/>
-      <c r="ADW2" s="12"/>
-      <c r="ADX2" s="12"/>
-      <c r="ADY2" s="12"/>
-      <c r="ADZ2" s="12"/>
-      <c r="AEA2" s="12"/>
-      <c r="AEB2" s="12"/>
-      <c r="AEC2" s="12"/>
-      <c r="AED2" s="12"/>
-      <c r="AEE2" s="12"/>
-      <c r="AEF2" s="12"/>
-      <c r="AEG2" s="12"/>
-      <c r="AEH2" s="12"/>
-      <c r="AEI2" s="12"/>
-      <c r="AEJ2" s="12"/>
-      <c r="AEK2" s="12"/>
-      <c r="AEL2" s="12"/>
-      <c r="AEM2" s="12"/>
-      <c r="AEN2" s="12"/>
-      <c r="AEO2" s="12"/>
-      <c r="AEP2" s="12"/>
-      <c r="AEQ2" s="12"/>
-      <c r="AER2" s="12"/>
-      <c r="AES2" s="12"/>
-      <c r="AET2" s="12"/>
-      <c r="AEU2" s="12"/>
-      <c r="AEV2" s="12"/>
-      <c r="AEW2" s="12"/>
-      <c r="AEX2" s="12"/>
-      <c r="AEY2" s="12"/>
-      <c r="AEZ2" s="12"/>
-      <c r="AFA2" s="12"/>
-      <c r="AFB2" s="12"/>
-      <c r="AFC2" s="12"/>
-      <c r="AFD2" s="12"/>
-      <c r="AFE2" s="12"/>
-      <c r="AFF2" s="12"/>
-      <c r="AFG2" s="12"/>
-      <c r="AFH2" s="12"/>
-      <c r="AFI2" s="12"/>
-      <c r="AFJ2" s="12"/>
-      <c r="AFK2" s="12"/>
-      <c r="AFL2" s="12"/>
-      <c r="AFM2" s="12"/>
-      <c r="AFN2" s="12"/>
-      <c r="AFO2" s="12"/>
-      <c r="AFP2" s="12"/>
-      <c r="AFQ2" s="12"/>
-      <c r="AFR2" s="12"/>
-      <c r="AFS2" s="12"/>
-      <c r="AFT2" s="12"/>
-      <c r="AFU2" s="12"/>
-      <c r="AFV2" s="12"/>
-      <c r="AFW2" s="12"/>
-      <c r="AFX2" s="12"/>
-      <c r="AFY2" s="12"/>
-      <c r="AFZ2" s="12"/>
-      <c r="AGA2" s="12"/>
-      <c r="AGB2" s="12"/>
-      <c r="AGC2" s="12"/>
-      <c r="AGD2" s="12"/>
-      <c r="AGE2" s="12"/>
-      <c r="AGF2" s="12"/>
-      <c r="AGG2" s="12"/>
-      <c r="AGH2" s="12"/>
-      <c r="AGI2" s="12"/>
-      <c r="AGJ2" s="12"/>
-      <c r="AGK2" s="12"/>
-      <c r="AGL2" s="12"/>
-      <c r="AGM2" s="12"/>
-      <c r="AGN2" s="12"/>
-      <c r="AGO2" s="12"/>
-      <c r="AGP2" s="12"/>
-      <c r="AGQ2" s="12"/>
-      <c r="AGR2" s="12"/>
-      <c r="AGS2" s="12"/>
-      <c r="AGT2" s="12"/>
-      <c r="AGU2" s="12"/>
-      <c r="AGV2" s="12"/>
-      <c r="AGW2" s="12"/>
-      <c r="AGX2" s="12"/>
-      <c r="AGY2" s="12"/>
-      <c r="AGZ2" s="12"/>
-      <c r="AHA2" s="12"/>
-      <c r="AHB2" s="12"/>
-      <c r="AHC2" s="12"/>
-      <c r="AHD2" s="12"/>
-      <c r="AHE2" s="12"/>
-      <c r="AHF2" s="12"/>
-      <c r="AHG2" s="12"/>
-      <c r="AHH2" s="12"/>
-      <c r="AHI2" s="12"/>
-      <c r="AHJ2" s="12"/>
-      <c r="AHK2" s="12"/>
-      <c r="AHL2" s="12"/>
-      <c r="AHM2" s="12"/>
-      <c r="AHN2" s="12"/>
-      <c r="AHO2" s="12"/>
-      <c r="AHP2" s="12"/>
-      <c r="AHQ2" s="12"/>
-      <c r="AHR2" s="12"/>
-      <c r="AHS2" s="12"/>
-      <c r="AHT2" s="12"/>
-      <c r="AHU2" s="12"/>
-      <c r="AHV2" s="12"/>
-      <c r="AHW2" s="12"/>
-      <c r="AHX2" s="12"/>
-      <c r="AHY2" s="12"/>
-      <c r="AHZ2" s="12"/>
-      <c r="AIA2" s="12"/>
-      <c r="AIB2" s="12"/>
-      <c r="AIC2" s="12"/>
-      <c r="AID2" s="12"/>
-      <c r="AIE2" s="12"/>
-      <c r="AIF2" s="12"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
+      <c r="AE2" s="11"/>
+      <c r="AF2" s="11"/>
+      <c r="AG2" s="11"/>
+      <c r="AH2" s="11"/>
+      <c r="AI2" s="11"/>
+      <c r="AJ2" s="11"/>
+      <c r="AK2" s="11"/>
+      <c r="AL2" s="11"/>
+      <c r="AM2" s="11"/>
+      <c r="AN2" s="11"/>
+      <c r="AO2" s="11"/>
+      <c r="AP2" s="11"/>
+      <c r="AQ2" s="11"/>
+      <c r="AR2" s="11"/>
+      <c r="AS2" s="11"/>
+      <c r="AT2" s="11"/>
+      <c r="AU2" s="11"/>
+      <c r="AV2" s="11"/>
+      <c r="AW2" s="11"/>
+      <c r="AX2" s="11"/>
+      <c r="AY2" s="11"/>
+      <c r="AZ2" s="11"/>
+      <c r="BA2" s="11"/>
+      <c r="BB2" s="11"/>
+      <c r="BC2" s="11"/>
+      <c r="BD2" s="11"/>
+      <c r="BE2" s="11"/>
+      <c r="BF2" s="11"/>
+      <c r="BG2" s="11"/>
+      <c r="BH2" s="11"/>
+      <c r="BI2" s="11"/>
+      <c r="BJ2" s="11"/>
+      <c r="BK2" s="11"/>
+      <c r="BL2" s="11"/>
+      <c r="BM2" s="11"/>
+      <c r="BN2" s="11"/>
+      <c r="BO2" s="11"/>
+      <c r="BP2" s="11"/>
+      <c r="BQ2" s="11"/>
+      <c r="BR2" s="11"/>
+      <c r="BS2" s="11"/>
+      <c r="BT2" s="11"/>
+      <c r="BU2" s="11"/>
+      <c r="BV2" s="11"/>
+      <c r="BW2" s="11"/>
+      <c r="BX2" s="11"/>
+      <c r="BY2" s="11"/>
+      <c r="BZ2" s="11"/>
+      <c r="CA2" s="11"/>
+      <c r="CB2" s="11"/>
+      <c r="CC2" s="11"/>
+      <c r="CD2" s="11"/>
+      <c r="CE2" s="11"/>
+      <c r="CF2" s="11"/>
+      <c r="CG2" s="11"/>
+      <c r="CH2" s="11"/>
+      <c r="CI2" s="11"/>
+      <c r="CJ2" s="11"/>
+      <c r="CK2" s="11"/>
+      <c r="CL2" s="11"/>
+      <c r="CM2" s="11"/>
+      <c r="CN2" s="11"/>
+      <c r="CO2" s="11"/>
+      <c r="CP2" s="11"/>
+      <c r="CQ2" s="11"/>
+      <c r="CR2" s="11"/>
+      <c r="CS2" s="11"/>
+      <c r="CT2" s="11"/>
+      <c r="CU2" s="11"/>
+      <c r="CV2" s="11"/>
+      <c r="CW2" s="11"/>
+      <c r="CX2" s="11"/>
+      <c r="CY2" s="11"/>
+      <c r="CZ2" s="11"/>
+      <c r="DA2" s="11"/>
+      <c r="DB2" s="11"/>
+      <c r="DC2" s="11"/>
+      <c r="DD2" s="11"/>
+      <c r="DE2" s="11"/>
+      <c r="DF2" s="11"/>
+      <c r="DG2" s="11"/>
+      <c r="DH2" s="11"/>
+      <c r="DI2" s="11"/>
+      <c r="DJ2" s="11"/>
+      <c r="DK2" s="11"/>
+      <c r="DL2" s="11"/>
+      <c r="DM2" s="11"/>
+      <c r="DN2" s="11"/>
+      <c r="DO2" s="11"/>
+      <c r="DP2" s="11"/>
+      <c r="DQ2" s="11"/>
+      <c r="DR2" s="11"/>
+      <c r="DS2" s="11"/>
+      <c r="DT2" s="11"/>
+      <c r="DU2" s="11"/>
+      <c r="DV2" s="11"/>
+      <c r="DW2" s="11"/>
+      <c r="DX2" s="11"/>
+      <c r="DY2" s="11"/>
+      <c r="DZ2" s="11"/>
+      <c r="EA2" s="11"/>
+      <c r="EB2" s="11"/>
+      <c r="EC2" s="11"/>
+      <c r="ED2" s="11"/>
+      <c r="EE2" s="11"/>
+      <c r="EF2" s="11"/>
+      <c r="EG2" s="11"/>
+      <c r="EH2" s="11"/>
+      <c r="EI2" s="11"/>
+      <c r="EJ2" s="11"/>
+      <c r="EK2" s="11"/>
+      <c r="EL2" s="11"/>
+      <c r="EM2" s="11"/>
+      <c r="EN2" s="11"/>
+      <c r="EO2" s="11"/>
+      <c r="EP2" s="11"/>
+      <c r="EQ2" s="11"/>
+      <c r="ER2" s="11"/>
+      <c r="ES2" s="11"/>
+      <c r="ET2" s="11"/>
+      <c r="EU2" s="11"/>
+      <c r="EV2" s="11"/>
+      <c r="EW2" s="11"/>
+      <c r="EX2" s="11"/>
+      <c r="EY2" s="11"/>
+      <c r="EZ2" s="11"/>
+      <c r="FA2" s="11"/>
+      <c r="FB2" s="11"/>
+      <c r="FC2" s="11"/>
+      <c r="FD2" s="11"/>
+      <c r="FE2" s="11"/>
+      <c r="FF2" s="11"/>
+      <c r="FG2" s="11"/>
+      <c r="FH2" s="11"/>
+      <c r="FI2" s="11"/>
+      <c r="FJ2" s="11"/>
+      <c r="FK2" s="11"/>
+      <c r="FL2" s="11"/>
+      <c r="FM2" s="11"/>
+      <c r="FN2" s="11"/>
+      <c r="FO2" s="11"/>
+      <c r="FP2" s="11"/>
+      <c r="FQ2" s="11"/>
+      <c r="FR2" s="11"/>
+      <c r="FS2" s="11"/>
+      <c r="FT2" s="11"/>
+      <c r="FU2" s="11"/>
+      <c r="FV2" s="11"/>
+      <c r="FW2" s="11"/>
+      <c r="FX2" s="11"/>
+      <c r="FY2" s="11"/>
+      <c r="FZ2" s="11"/>
+      <c r="GA2" s="11"/>
+      <c r="GB2" s="11"/>
+      <c r="GC2" s="11"/>
+      <c r="GD2" s="11"/>
+      <c r="GE2" s="11"/>
+      <c r="GF2" s="11"/>
+      <c r="GG2" s="11"/>
+      <c r="GH2" s="11"/>
+      <c r="GI2" s="11"/>
+      <c r="GJ2" s="11"/>
+      <c r="GK2" s="11"/>
+      <c r="GL2" s="11"/>
+      <c r="GM2" s="11"/>
+      <c r="GN2" s="11"/>
+      <c r="GO2" s="11"/>
+      <c r="GP2" s="11"/>
+      <c r="GQ2" s="11"/>
+      <c r="GR2" s="11"/>
+      <c r="GS2" s="11"/>
+      <c r="GT2" s="11"/>
+      <c r="GU2" s="11"/>
+      <c r="GV2" s="11"/>
+      <c r="GW2" s="11"/>
+      <c r="GX2" s="11"/>
+      <c r="GY2" s="11"/>
+      <c r="GZ2" s="11"/>
+      <c r="HA2" s="11"/>
+      <c r="HB2" s="11"/>
+      <c r="HC2" s="11"/>
+      <c r="HD2" s="11"/>
+      <c r="HE2" s="11"/>
+      <c r="HF2" s="11"/>
+      <c r="HG2" s="11"/>
+      <c r="HH2" s="11"/>
+      <c r="HI2" s="11"/>
+      <c r="HJ2" s="11"/>
+      <c r="HK2" s="11"/>
+      <c r="HL2" s="11"/>
+      <c r="HM2" s="11"/>
+      <c r="HN2" s="11"/>
+      <c r="HO2" s="11"/>
+      <c r="HP2" s="11"/>
+      <c r="HQ2" s="11"/>
+      <c r="HR2" s="11"/>
+      <c r="HS2" s="11"/>
+      <c r="HT2" s="11"/>
+      <c r="HU2" s="11"/>
+      <c r="HV2" s="11"/>
+      <c r="HW2" s="11"/>
+      <c r="HX2" s="11"/>
+      <c r="HY2" s="11"/>
+      <c r="HZ2" s="11"/>
+      <c r="IA2" s="11"/>
+      <c r="IB2" s="11"/>
+      <c r="IC2" s="11"/>
+      <c r="ID2" s="11"/>
+      <c r="IE2" s="11"/>
+      <c r="IF2" s="11"/>
+      <c r="IG2" s="11"/>
+      <c r="IH2" s="11"/>
+      <c r="II2" s="11"/>
+      <c r="IJ2" s="11"/>
+      <c r="IK2" s="11"/>
+      <c r="IL2" s="11"/>
+      <c r="IM2" s="11"/>
+      <c r="IN2" s="11"/>
+      <c r="IO2" s="11"/>
+      <c r="IP2" s="11"/>
+      <c r="IQ2" s="11"/>
+      <c r="IR2" s="11"/>
+      <c r="IS2" s="11"/>
+      <c r="IT2" s="11"/>
+      <c r="IU2" s="11"/>
+      <c r="IV2" s="11"/>
+      <c r="IW2" s="11"/>
+      <c r="IX2" s="11"/>
+      <c r="IY2" s="11"/>
+      <c r="IZ2" s="11"/>
+      <c r="JA2" s="11"/>
+      <c r="JB2" s="11"/>
+      <c r="JC2" s="11"/>
+      <c r="JD2" s="11"/>
+      <c r="JE2" s="11"/>
+      <c r="JF2" s="11"/>
+      <c r="JG2" s="11"/>
+      <c r="JH2" s="11"/>
+      <c r="JI2" s="11"/>
+      <c r="JJ2" s="11"/>
+      <c r="JK2" s="11"/>
+      <c r="JL2" s="11"/>
+      <c r="JM2" s="11"/>
+      <c r="JN2" s="11"/>
+      <c r="JO2" s="11"/>
+      <c r="JP2" s="11"/>
+      <c r="JQ2" s="11"/>
+      <c r="JR2" s="11"/>
+      <c r="JS2" s="11"/>
+      <c r="JT2" s="11"/>
+      <c r="JU2" s="11"/>
+      <c r="JV2" s="11"/>
+      <c r="JW2" s="11"/>
+      <c r="JX2" s="11"/>
+      <c r="JY2" s="11"/>
+      <c r="JZ2" s="11"/>
+      <c r="KA2" s="11"/>
+      <c r="KB2" s="11"/>
+      <c r="KC2" s="11"/>
+      <c r="KD2" s="11"/>
+      <c r="KE2" s="11"/>
+      <c r="KF2" s="11"/>
+      <c r="KG2" s="11"/>
+      <c r="KH2" s="11"/>
+      <c r="KI2" s="11"/>
+      <c r="KJ2" s="11"/>
+      <c r="KK2" s="11"/>
+      <c r="KL2" s="11"/>
+      <c r="KM2" s="11"/>
+      <c r="KN2" s="11"/>
+      <c r="KO2" s="11"/>
+      <c r="KP2" s="11"/>
+      <c r="KQ2" s="11"/>
+      <c r="KR2" s="11"/>
+      <c r="KS2" s="11"/>
+      <c r="KT2" s="11"/>
+      <c r="KU2" s="11"/>
+      <c r="KV2" s="11"/>
+      <c r="KW2" s="11"/>
+      <c r="KX2" s="11"/>
+      <c r="KY2" s="11"/>
+      <c r="KZ2" s="11"/>
+      <c r="LA2" s="11"/>
+      <c r="LB2" s="11"/>
+      <c r="LC2" s="11"/>
+      <c r="LD2" s="11"/>
+      <c r="LE2" s="11"/>
+      <c r="LF2" s="11"/>
+      <c r="LG2" s="11"/>
+      <c r="LH2" s="11"/>
+      <c r="LI2" s="11"/>
+      <c r="LJ2" s="11"/>
+      <c r="LK2" s="11"/>
+      <c r="LL2" s="11"/>
+      <c r="LM2" s="11"/>
+      <c r="LN2" s="11"/>
+      <c r="LO2" s="11"/>
+      <c r="LP2" s="11"/>
+      <c r="LQ2" s="11"/>
+      <c r="LR2" s="11"/>
+      <c r="LS2" s="11"/>
+      <c r="LT2" s="11"/>
+      <c r="LU2" s="11"/>
+      <c r="LV2" s="11"/>
+      <c r="LW2" s="11"/>
+      <c r="LX2" s="11"/>
+      <c r="LY2" s="11"/>
+      <c r="LZ2" s="11"/>
+      <c r="MA2" s="11"/>
+      <c r="MB2" s="11"/>
+      <c r="MC2" s="11"/>
+      <c r="MD2" s="11"/>
+      <c r="ME2" s="11"/>
+      <c r="MF2" s="11"/>
+      <c r="MG2" s="11"/>
+      <c r="MH2" s="11"/>
+      <c r="MI2" s="11"/>
+      <c r="MJ2" s="11"/>
+      <c r="MK2" s="11"/>
+      <c r="ML2" s="11"/>
+      <c r="MM2" s="11"/>
+      <c r="MN2" s="11"/>
+      <c r="MO2" s="11"/>
+      <c r="MP2" s="11"/>
+      <c r="MQ2" s="11"/>
+      <c r="MR2" s="11"/>
+      <c r="MS2" s="11"/>
+      <c r="MT2" s="11"/>
+      <c r="MU2" s="11"/>
+      <c r="MV2" s="11"/>
+      <c r="MW2" s="11"/>
+      <c r="MX2" s="11"/>
+      <c r="MY2" s="11"/>
+      <c r="MZ2" s="11"/>
+      <c r="NA2" s="11"/>
+      <c r="NB2" s="11"/>
+      <c r="NC2" s="11"/>
+      <c r="ND2" s="11"/>
+      <c r="NE2" s="11"/>
+      <c r="NF2" s="11"/>
+      <c r="NG2" s="11"/>
+      <c r="NH2" s="11"/>
+      <c r="NI2" s="11"/>
+      <c r="NJ2" s="11"/>
+      <c r="NK2" s="11"/>
+      <c r="NL2" s="11"/>
+      <c r="NM2" s="11"/>
+      <c r="NN2" s="11"/>
+      <c r="NO2" s="11"/>
+      <c r="NP2" s="11"/>
+      <c r="NQ2" s="11"/>
+      <c r="NR2" s="11"/>
+      <c r="NS2" s="11"/>
+      <c r="NT2" s="11"/>
+      <c r="NU2" s="11"/>
+      <c r="NV2" s="11"/>
+      <c r="NW2" s="11"/>
+      <c r="NX2" s="11"/>
+      <c r="NY2" s="11"/>
+      <c r="NZ2" s="11"/>
+      <c r="OA2" s="11"/>
+      <c r="OB2" s="11"/>
+      <c r="OC2" s="11"/>
+      <c r="OD2" s="11"/>
+      <c r="OE2" s="11"/>
+      <c r="OF2" s="11"/>
+      <c r="OG2" s="11"/>
+      <c r="OH2" s="11"/>
+      <c r="OI2" s="11"/>
+      <c r="OJ2" s="11"/>
+      <c r="OK2" s="11"/>
+      <c r="OL2" s="11"/>
+      <c r="OM2" s="11"/>
+      <c r="ON2" s="11"/>
+      <c r="OO2" s="11"/>
+      <c r="OP2" s="11"/>
+      <c r="OQ2" s="11"/>
+      <c r="OR2" s="11"/>
+      <c r="OS2" s="11"/>
+      <c r="OT2" s="11"/>
+      <c r="OU2" s="11"/>
+      <c r="OV2" s="11"/>
+      <c r="OW2" s="11"/>
+      <c r="OX2" s="11"/>
+      <c r="OY2" s="11"/>
+      <c r="OZ2" s="11"/>
+      <c r="PA2" s="11"/>
+      <c r="PB2" s="11"/>
+      <c r="PC2" s="11"/>
+      <c r="PD2" s="11"/>
+      <c r="PE2" s="11"/>
+      <c r="PF2" s="11"/>
+      <c r="PG2" s="11"/>
+      <c r="PH2" s="11"/>
+      <c r="PI2" s="11"/>
+      <c r="PJ2" s="11"/>
+      <c r="PK2" s="11"/>
+      <c r="PL2" s="11"/>
+      <c r="PM2" s="11"/>
+      <c r="PN2" s="11"/>
+      <c r="PO2" s="11"/>
+      <c r="PP2" s="11"/>
+      <c r="PQ2" s="11"/>
+      <c r="PR2" s="11"/>
+      <c r="PS2" s="11"/>
+      <c r="PT2" s="11"/>
+      <c r="PU2" s="11"/>
+      <c r="PV2" s="11"/>
+      <c r="PW2" s="11"/>
+      <c r="PX2" s="11"/>
+      <c r="PY2" s="11"/>
+      <c r="PZ2" s="11"/>
+      <c r="QA2" s="11"/>
+      <c r="QB2" s="11"/>
+      <c r="QC2" s="11"/>
+      <c r="QD2" s="11"/>
+      <c r="QE2" s="11"/>
+      <c r="QF2" s="11"/>
+      <c r="QG2" s="11"/>
+      <c r="QH2" s="11"/>
+      <c r="QI2" s="11"/>
+      <c r="QJ2" s="11"/>
+      <c r="QK2" s="11"/>
+      <c r="QL2" s="11"/>
+      <c r="QM2" s="11"/>
+      <c r="QN2" s="11"/>
+      <c r="QO2" s="11"/>
+      <c r="QP2" s="11"/>
+      <c r="QQ2" s="11"/>
+      <c r="QR2" s="11"/>
+      <c r="QS2" s="11"/>
+      <c r="QT2" s="11"/>
+      <c r="QU2" s="11"/>
+      <c r="QV2" s="11"/>
+      <c r="QW2" s="11"/>
+      <c r="QX2" s="11"/>
+      <c r="QY2" s="11"/>
+      <c r="QZ2" s="11"/>
+      <c r="RA2" s="11"/>
+      <c r="RB2" s="11"/>
+      <c r="RC2" s="11"/>
+      <c r="RD2" s="11"/>
+      <c r="RE2" s="11"/>
+      <c r="RF2" s="11"/>
+      <c r="RG2" s="11"/>
+      <c r="RH2" s="11"/>
+      <c r="RI2" s="11"/>
+      <c r="RJ2" s="11"/>
+      <c r="RK2" s="11"/>
+      <c r="RL2" s="11"/>
+      <c r="RM2" s="11"/>
+      <c r="RN2" s="11"/>
+      <c r="RO2" s="11"/>
+      <c r="RP2" s="11"/>
+      <c r="RQ2" s="11"/>
+      <c r="RR2" s="11"/>
+      <c r="RS2" s="11"/>
+      <c r="RT2" s="11"/>
+      <c r="RU2" s="11"/>
+      <c r="RV2" s="11"/>
+      <c r="RW2" s="11"/>
+      <c r="RX2" s="11"/>
+      <c r="RY2" s="11"/>
+      <c r="RZ2" s="11"/>
+      <c r="SA2" s="11"/>
+      <c r="SB2" s="11"/>
+      <c r="SC2" s="11"/>
+      <c r="SD2" s="11"/>
+      <c r="SE2" s="11"/>
+      <c r="SF2" s="11"/>
+      <c r="SG2" s="11"/>
+      <c r="SH2" s="11"/>
+      <c r="SI2" s="11"/>
+      <c r="SJ2" s="11"/>
+      <c r="SK2" s="11"/>
+      <c r="SL2" s="11"/>
+      <c r="SM2" s="11"/>
+      <c r="SN2" s="11"/>
+      <c r="SO2" s="11"/>
+      <c r="SP2" s="11"/>
+      <c r="SQ2" s="11"/>
+      <c r="SR2" s="11"/>
+      <c r="SS2" s="11"/>
+      <c r="ST2" s="11"/>
+      <c r="SU2" s="11"/>
+      <c r="SV2" s="11"/>
+      <c r="SW2" s="11"/>
+      <c r="SX2" s="11"/>
+      <c r="SY2" s="11"/>
+      <c r="SZ2" s="11"/>
+      <c r="TA2" s="11"/>
+      <c r="TB2" s="11"/>
+      <c r="TC2" s="11"/>
+      <c r="TD2" s="11"/>
+      <c r="TE2" s="11"/>
+      <c r="TF2" s="11"/>
+      <c r="TG2" s="11"/>
+      <c r="TH2" s="11"/>
+      <c r="TI2" s="11"/>
+      <c r="TJ2" s="11"/>
+      <c r="TK2" s="11"/>
+      <c r="TL2" s="11"/>
+      <c r="TM2" s="11"/>
+      <c r="TN2" s="11"/>
+      <c r="TO2" s="11"/>
+      <c r="TP2" s="11"/>
+      <c r="TQ2" s="11"/>
+      <c r="TR2" s="11"/>
+      <c r="TS2" s="11"/>
+      <c r="TT2" s="11"/>
+      <c r="TU2" s="11"/>
+      <c r="TV2" s="11"/>
+      <c r="TW2" s="11"/>
+      <c r="TX2" s="11"/>
+      <c r="TY2" s="11"/>
+      <c r="TZ2" s="11"/>
+      <c r="UA2" s="11"/>
+      <c r="UB2" s="11"/>
+      <c r="UC2" s="11"/>
+      <c r="UD2" s="11"/>
+      <c r="UE2" s="11"/>
+      <c r="UF2" s="11"/>
+      <c r="UG2" s="11"/>
+      <c r="UH2" s="11"/>
+      <c r="UI2" s="11"/>
+      <c r="UJ2" s="11"/>
+      <c r="UK2" s="11"/>
+      <c r="UL2" s="11"/>
+      <c r="UM2" s="11"/>
+      <c r="UN2" s="11"/>
+      <c r="UO2" s="11"/>
+      <c r="UP2" s="11"/>
+      <c r="UQ2" s="11"/>
+      <c r="UR2" s="11"/>
+      <c r="US2" s="11"/>
+      <c r="UT2" s="11"/>
+      <c r="UU2" s="11"/>
+      <c r="UV2" s="11"/>
+      <c r="UW2" s="11"/>
+      <c r="UX2" s="11"/>
+      <c r="UY2" s="11"/>
+      <c r="UZ2" s="11"/>
+      <c r="VA2" s="11"/>
+      <c r="VB2" s="11"/>
+      <c r="VC2" s="11"/>
+      <c r="VD2" s="11"/>
+      <c r="VE2" s="11"/>
+      <c r="VF2" s="11"/>
+      <c r="VG2" s="11"/>
+      <c r="VH2" s="11"/>
+      <c r="VI2" s="11"/>
+      <c r="VJ2" s="11"/>
+      <c r="VK2" s="11"/>
+      <c r="VL2" s="11"/>
+      <c r="VM2" s="11"/>
+      <c r="VN2" s="11"/>
+      <c r="VO2" s="11"/>
+      <c r="VP2" s="11"/>
+      <c r="VQ2" s="11"/>
+      <c r="VR2" s="11"/>
+      <c r="VS2" s="11"/>
+      <c r="VT2" s="11"/>
+      <c r="VU2" s="11"/>
+      <c r="VV2" s="11"/>
+      <c r="VW2" s="11"/>
+      <c r="VX2" s="11"/>
+      <c r="VY2" s="11"/>
+      <c r="VZ2" s="11"/>
+      <c r="WA2" s="11"/>
+      <c r="WB2" s="11"/>
+      <c r="WC2" s="11"/>
+      <c r="WD2" s="11"/>
+      <c r="WE2" s="11"/>
+      <c r="WF2" s="11"/>
+      <c r="WG2" s="11"/>
+      <c r="WH2" s="11"/>
+      <c r="WI2" s="11"/>
+      <c r="WJ2" s="11"/>
+      <c r="WK2" s="11"/>
+      <c r="WL2" s="11"/>
+      <c r="WM2" s="11"/>
+      <c r="WN2" s="11"/>
+      <c r="WO2" s="11"/>
+      <c r="WP2" s="11"/>
+      <c r="WQ2" s="11"/>
+      <c r="WR2" s="11"/>
+      <c r="WS2" s="11"/>
+      <c r="WT2" s="11"/>
+      <c r="WU2" s="11"/>
+      <c r="WV2" s="11"/>
+      <c r="WW2" s="11"/>
+      <c r="WX2" s="11"/>
+      <c r="WY2" s="11"/>
+      <c r="WZ2" s="11"/>
+      <c r="XA2" s="11"/>
+      <c r="XB2" s="11"/>
+      <c r="XC2" s="11"/>
+      <c r="XD2" s="11"/>
+      <c r="XE2" s="11"/>
+      <c r="XF2" s="11"/>
+      <c r="XG2" s="11"/>
+      <c r="XH2" s="11"/>
+      <c r="XI2" s="11"/>
+      <c r="XJ2" s="11"/>
+      <c r="XK2" s="11"/>
+      <c r="XL2" s="11"/>
+      <c r="XM2" s="11"/>
+      <c r="XN2" s="11"/>
+      <c r="XO2" s="11"/>
+      <c r="XP2" s="11"/>
+      <c r="XQ2" s="11"/>
+      <c r="XR2" s="11"/>
+      <c r="XS2" s="11"/>
+      <c r="XT2" s="11"/>
+      <c r="XU2" s="11"/>
+      <c r="XV2" s="11"/>
+      <c r="XW2" s="11"/>
+      <c r="XX2" s="11"/>
+      <c r="XY2" s="11"/>
+      <c r="XZ2" s="11"/>
+      <c r="YA2" s="11"/>
+      <c r="YB2" s="11"/>
+      <c r="YC2" s="11"/>
+      <c r="YD2" s="11"/>
+      <c r="YE2" s="11"/>
+      <c r="YF2" s="11"/>
+      <c r="YG2" s="11"/>
+      <c r="YH2" s="11"/>
+      <c r="YI2" s="11"/>
+      <c r="YJ2" s="11"/>
+      <c r="YK2" s="11"/>
+      <c r="YL2" s="11"/>
+      <c r="YM2" s="11"/>
+      <c r="YN2" s="11"/>
+      <c r="YO2" s="11"/>
+      <c r="YP2" s="11"/>
+      <c r="YQ2" s="11"/>
+      <c r="YR2" s="11"/>
+      <c r="YS2" s="11"/>
+      <c r="YT2" s="11"/>
+      <c r="YU2" s="11"/>
+      <c r="YV2" s="11"/>
+      <c r="YW2" s="11"/>
+      <c r="YX2" s="11"/>
+      <c r="YY2" s="11"/>
+      <c r="YZ2" s="11"/>
+      <c r="ZA2" s="11"/>
+      <c r="ZB2" s="11"/>
+      <c r="ZC2" s="11"/>
+      <c r="ZD2" s="11"/>
+      <c r="ZE2" s="11"/>
+      <c r="ZF2" s="11"/>
+      <c r="ZG2" s="11"/>
+      <c r="ZH2" s="11"/>
+      <c r="ZI2" s="11"/>
+      <c r="ZJ2" s="11"/>
+      <c r="ZK2" s="11"/>
+      <c r="ZL2" s="11"/>
+      <c r="ZM2" s="11"/>
+      <c r="ZN2" s="11"/>
+      <c r="ZO2" s="11"/>
+      <c r="ZP2" s="11"/>
+      <c r="ZQ2" s="11"/>
+      <c r="ZR2" s="11"/>
+      <c r="ZS2" s="11"/>
+      <c r="ZT2" s="11"/>
+      <c r="ZU2" s="11"/>
+      <c r="ZV2" s="11"/>
+      <c r="ZW2" s="11"/>
+      <c r="ZX2" s="11"/>
+      <c r="ZY2" s="11"/>
+      <c r="ZZ2" s="11"/>
+      <c r="AAA2" s="11"/>
+      <c r="AAB2" s="11"/>
+      <c r="AAC2" s="11"/>
+      <c r="AAD2" s="11"/>
+      <c r="AAE2" s="11"/>
+      <c r="AAF2" s="11"/>
+      <c r="AAG2" s="11"/>
+      <c r="AAH2" s="11"/>
+      <c r="AAI2" s="11"/>
+      <c r="AAJ2" s="11"/>
+      <c r="AAK2" s="11"/>
+      <c r="AAL2" s="11"/>
+      <c r="AAM2" s="11"/>
+      <c r="AAN2" s="11"/>
+      <c r="AAO2" s="11"/>
+      <c r="AAP2" s="11"/>
+      <c r="AAQ2" s="11"/>
+      <c r="AAR2" s="11"/>
+      <c r="AAS2" s="11"/>
+      <c r="AAT2" s="11"/>
+      <c r="AAU2" s="11"/>
+      <c r="AAV2" s="11"/>
+      <c r="AAW2" s="11"/>
+      <c r="AAX2" s="11"/>
+      <c r="AAY2" s="11"/>
+      <c r="AAZ2" s="11"/>
+      <c r="ABA2" s="11"/>
+      <c r="ABB2" s="11"/>
+      <c r="ABC2" s="11"/>
+      <c r="ABD2" s="11"/>
+      <c r="ABE2" s="11"/>
+      <c r="ABF2" s="11"/>
+      <c r="ABG2" s="11"/>
+      <c r="ABH2" s="11"/>
+      <c r="ABI2" s="11"/>
+      <c r="ABJ2" s="11"/>
+      <c r="ABK2" s="11"/>
+      <c r="ABL2" s="11"/>
+      <c r="ABM2" s="11"/>
+      <c r="ABN2" s="11"/>
+      <c r="ABO2" s="11"/>
+      <c r="ABP2" s="11"/>
+      <c r="ABQ2" s="11"/>
+      <c r="ABR2" s="11"/>
+      <c r="ABS2" s="11"/>
+      <c r="ABT2" s="11"/>
+      <c r="ABU2" s="11"/>
+      <c r="ABV2" s="11"/>
+      <c r="ABW2" s="11"/>
+      <c r="ABX2" s="11"/>
+      <c r="ABY2" s="11"/>
+      <c r="ABZ2" s="11"/>
+      <c r="ACA2" s="11"/>
+      <c r="ACB2" s="11"/>
+      <c r="ACC2" s="11"/>
+      <c r="ACD2" s="11"/>
+      <c r="ACE2" s="11"/>
+      <c r="ACF2" s="11"/>
+      <c r="ACG2" s="11"/>
+      <c r="ACH2" s="11"/>
+      <c r="ACI2" s="11"/>
+      <c r="ACJ2" s="11"/>
+      <c r="ACK2" s="11"/>
+      <c r="ACL2" s="11"/>
+      <c r="ACM2" s="11"/>
+      <c r="ACN2" s="11"/>
+      <c r="ACO2" s="11"/>
+      <c r="ACP2" s="11"/>
+      <c r="ACQ2" s="11"/>
+      <c r="ACR2" s="11"/>
+      <c r="ACS2" s="11"/>
+      <c r="ACT2" s="11"/>
+      <c r="ACU2" s="11"/>
+      <c r="ACV2" s="11"/>
+      <c r="ACW2" s="11"/>
+      <c r="ACX2" s="11"/>
+      <c r="ACY2" s="11"/>
+      <c r="ACZ2" s="11"/>
+      <c r="ADA2" s="11"/>
+      <c r="ADB2" s="11"/>
+      <c r="ADC2" s="11"/>
+      <c r="ADD2" s="11"/>
+      <c r="ADE2" s="11"/>
+      <c r="ADF2" s="11"/>
+      <c r="ADG2" s="11"/>
+      <c r="ADH2" s="11"/>
+      <c r="ADI2" s="11"/>
+      <c r="ADJ2" s="11"/>
+      <c r="ADK2" s="11"/>
+      <c r="ADL2" s="11"/>
+      <c r="ADM2" s="11"/>
+      <c r="ADN2" s="11"/>
+      <c r="ADO2" s="11"/>
+      <c r="ADP2" s="11"/>
+      <c r="ADQ2" s="11"/>
+      <c r="ADR2" s="11"/>
+      <c r="ADS2" s="11"/>
+      <c r="ADT2" s="11"/>
+      <c r="ADU2" s="11"/>
+      <c r="ADV2" s="11"/>
+      <c r="ADW2" s="11"/>
+      <c r="ADX2" s="11"/>
+      <c r="ADY2" s="11"/>
+      <c r="ADZ2" s="11"/>
+      <c r="AEA2" s="11"/>
+      <c r="AEB2" s="11"/>
+      <c r="AEC2" s="11"/>
+      <c r="AED2" s="11"/>
+      <c r="AEE2" s="11"/>
+      <c r="AEF2" s="11"/>
+      <c r="AEG2" s="11"/>
+      <c r="AEH2" s="11"/>
+      <c r="AEI2" s="11"/>
+      <c r="AEJ2" s="11"/>
+      <c r="AEK2" s="11"/>
+      <c r="AEL2" s="11"/>
+      <c r="AEM2" s="11"/>
+      <c r="AEN2" s="11"/>
+      <c r="AEO2" s="11"/>
+      <c r="AEP2" s="11"/>
+      <c r="AEQ2" s="11"/>
+      <c r="AER2" s="11"/>
+      <c r="AES2" s="11"/>
+      <c r="AET2" s="11"/>
+      <c r="AEU2" s="11"/>
+      <c r="AEV2" s="11"/>
+      <c r="AEW2" s="11"/>
+      <c r="AEX2" s="11"/>
+      <c r="AEY2" s="11"/>
+      <c r="AEZ2" s="11"/>
+      <c r="AFA2" s="11"/>
+      <c r="AFB2" s="11"/>
+      <c r="AFC2" s="11"/>
+      <c r="AFD2" s="11"/>
+      <c r="AFE2" s="11"/>
+      <c r="AFF2" s="11"/>
+      <c r="AFG2" s="11"/>
+      <c r="AFH2" s="11"/>
+      <c r="AFI2" s="11"/>
+      <c r="AFJ2" s="11"/>
+      <c r="AFK2" s="11"/>
+      <c r="AFL2" s="11"/>
+      <c r="AFM2" s="11"/>
+      <c r="AFN2" s="11"/>
+      <c r="AFO2" s="11"/>
+      <c r="AFP2" s="11"/>
+      <c r="AFQ2" s="11"/>
+      <c r="AFR2" s="11"/>
+      <c r="AFS2" s="11"/>
+      <c r="AFT2" s="11"/>
+      <c r="AFU2" s="11"/>
+      <c r="AFV2" s="11"/>
+      <c r="AFW2" s="11"/>
+      <c r="AFX2" s="11"/>
+      <c r="AFY2" s="11"/>
+      <c r="AFZ2" s="11"/>
+      <c r="AGA2" s="11"/>
+      <c r="AGB2" s="11"/>
+      <c r="AGC2" s="11"/>
+      <c r="AGD2" s="11"/>
+      <c r="AGE2" s="11"/>
+      <c r="AGF2" s="11"/>
+      <c r="AGG2" s="11"/>
+      <c r="AGH2" s="11"/>
+      <c r="AGI2" s="11"/>
+      <c r="AGJ2" s="11"/>
+      <c r="AGK2" s="11"/>
+      <c r="AGL2" s="11"/>
+      <c r="AGM2" s="11"/>
+      <c r="AGN2" s="11"/>
+      <c r="AGO2" s="11"/>
+      <c r="AGP2" s="11"/>
+      <c r="AGQ2" s="11"/>
+      <c r="AGR2" s="11"/>
+      <c r="AGS2" s="11"/>
+      <c r="AGT2" s="11"/>
+      <c r="AGU2" s="11"/>
+      <c r="AGV2" s="11"/>
+      <c r="AGW2" s="11"/>
+      <c r="AGX2" s="11"/>
+      <c r="AGY2" s="11"/>
+      <c r="AGZ2" s="11"/>
+      <c r="AHA2" s="11"/>
+      <c r="AHB2" s="11"/>
+      <c r="AHC2" s="11"/>
+      <c r="AHD2" s="11"/>
+      <c r="AHE2" s="11"/>
+      <c r="AHF2" s="11"/>
+      <c r="AHG2" s="11"/>
+      <c r="AHH2" s="11"/>
+      <c r="AHI2" s="11"/>
+      <c r="AHJ2" s="11"/>
+      <c r="AHK2" s="11"/>
+      <c r="AHL2" s="11"/>
+      <c r="AHM2" s="11"/>
+      <c r="AHN2" s="11"/>
+      <c r="AHO2" s="11"/>
+      <c r="AHP2" s="11"/>
+      <c r="AHQ2" s="11"/>
+      <c r="AHR2" s="11"/>
+      <c r="AHS2" s="11"/>
+      <c r="AHT2" s="11"/>
+      <c r="AHU2" s="11"/>
+      <c r="AHV2" s="11"/>
+      <c r="AHW2" s="11"/>
+      <c r="AHX2" s="11"/>
+      <c r="AHY2" s="11"/>
+      <c r="AHZ2" s="11"/>
+      <c r="AIA2" s="11"/>
+      <c r="AIB2" s="11"/>
+      <c r="AIC2" s="11"/>
+      <c r="AID2" s="11"/>
+      <c r="AIE2" s="11"/>
+      <c r="AIF2" s="11"/>
     </row>
     <row r="3" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="51"/>
-      <c r="P3" s="56">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="75"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="48">
         <f>C3*0.5+F3*0.2+I3*0.1+M3*0.2</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="52"/>
-      <c r="R3" s="53"/>
-      <c r="S3" s="53"/>
-      <c r="T3" s="54"/>
-      <c r="U3" s="54"/>
-      <c r="V3" s="54"/>
-      <c r="W3" s="54"/>
-      <c r="X3" s="55"/>
+      <c r="Q3" s="44"/>
+      <c r="R3" s="45"/>
+      <c r="S3" s="45"/>
+      <c r="T3" s="46"/>
+      <c r="U3" s="46"/>
+      <c r="V3" s="46"/>
+      <c r="W3" s="46"/>
+      <c r="X3" s="47"/>
     </row>
     <row r="4" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="51"/>
-      <c r="N4" s="51"/>
-      <c r="O4" s="51"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="52"/>
-      <c r="R4" s="53"/>
-      <c r="S4" s="53"/>
-      <c r="T4" s="54"/>
-      <c r="U4" s="54"/>
-      <c r="V4" s="54"/>
-      <c r="W4" s="54"/>
-      <c r="X4" s="55"/>
-      <c r="Y4" s="57"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="75"/>
+      <c r="M4" s="75"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="45"/>
+      <c r="S4" s="45"/>
+      <c r="T4" s="46"/>
+      <c r="U4" s="46"/>
+      <c r="V4" s="46"/>
+      <c r="W4" s="46"/>
+      <c r="X4" s="47"/>
+      <c r="Y4" s="49"/>
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="51"/>
-      <c r="N5" s="51"/>
-      <c r="O5" s="51"/>
-      <c r="P5" s="56"/>
-      <c r="Q5" s="52"/>
-      <c r="R5" s="53"/>
-      <c r="S5" s="53"/>
-      <c r="T5" s="54"/>
-      <c r="U5" s="54"/>
-      <c r="V5" s="54"/>
-      <c r="W5" s="54"/>
-      <c r="X5" s="55"/>
+      <c r="A5" s="22"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="75"/>
+      <c r="M5" s="75"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="44"/>
+      <c r="R5" s="45"/>
+      <c r="S5" s="45"/>
+      <c r="T5" s="46"/>
+      <c r="U5" s="46"/>
+      <c r="V5" s="46"/>
+      <c r="W5" s="46"/>
+      <c r="X5" s="47"/>
     </row>
     <row r="6" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="51"/>
-      <c r="P6" s="56"/>
-      <c r="Q6" s="52"/>
-      <c r="R6" s="53"/>
-      <c r="S6" s="53"/>
-      <c r="T6" s="54"/>
-      <c r="U6" s="54"/>
-      <c r="V6" s="54"/>
-      <c r="W6" s="54"/>
-      <c r="X6" s="55"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="75"/>
+      <c r="M6" s="75"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="44"/>
+      <c r="R6" s="45"/>
+      <c r="S6" s="45"/>
+      <c r="T6" s="46"/>
+      <c r="U6" s="46"/>
+      <c r="V6" s="46"/>
+      <c r="W6" s="46"/>
+      <c r="X6" s="47"/>
     </row>
     <row r="7" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="24"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="51"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51"/>
-      <c r="P7" s="56"/>
-      <c r="Q7" s="52"/>
-      <c r="R7" s="53"/>
-      <c r="S7" s="53"/>
-      <c r="T7" s="54"/>
-      <c r="U7" s="54"/>
-      <c r="V7" s="54"/>
-      <c r="W7" s="54"/>
-      <c r="X7" s="55"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="75"/>
+      <c r="M7" s="75"/>
+      <c r="N7" s="43"/>
+      <c r="O7" s="43"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="44"/>
+      <c r="R7" s="45"/>
+      <c r="S7" s="45"/>
+      <c r="T7" s="46"/>
+      <c r="U7" s="46"/>
+      <c r="V7" s="46"/>
+      <c r="W7" s="46"/>
+      <c r="X7" s="47"/>
       <c r="Y7" s="4"/>
       <c r="Z7" s="5"/>
       <c r="AA7" s="5"/>
@@ -2879,56 +2908,56 @@
       <c r="AIF7" s="5"/>
     </row>
     <row r="8" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="51"/>
-      <c r="P8" s="56"/>
-      <c r="Q8" s="52"/>
-      <c r="R8" s="53"/>
-      <c r="S8" s="53"/>
-      <c r="T8" s="54"/>
-      <c r="U8" s="54"/>
-      <c r="V8" s="54"/>
-      <c r="W8" s="54"/>
-      <c r="X8" s="55"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="75"/>
+      <c r="M8" s="75"/>
+      <c r="N8" s="43"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="44"/>
+      <c r="R8" s="45"/>
+      <c r="S8" s="45"/>
+      <c r="T8" s="46"/>
+      <c r="U8" s="46"/>
+      <c r="V8" s="46"/>
+      <c r="W8" s="46"/>
+      <c r="X8" s="47"/>
     </row>
     <row r="9" spans="1:917" s="6" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="24"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="51"/>
-      <c r="N9" s="51"/>
-      <c r="O9" s="51"/>
-      <c r="P9" s="56"/>
-      <c r="Q9" s="52"/>
-      <c r="R9" s="53"/>
-      <c r="S9" s="53"/>
-      <c r="T9" s="54"/>
-      <c r="U9" s="54"/>
-      <c r="V9" s="54"/>
-      <c r="W9" s="54"/>
-      <c r="X9" s="55"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="75"/>
+      <c r="M9" s="75"/>
+      <c r="N9" s="43"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="44"/>
+      <c r="R9" s="45"/>
+      <c r="S9" s="45"/>
+      <c r="T9" s="46"/>
+      <c r="U9" s="46"/>
+      <c r="V9" s="46"/>
+      <c r="W9" s="46"/>
+      <c r="X9" s="47"/>
       <c r="Y9" s="4"/>
       <c r="Z9" s="5"/>
       <c r="AA9" s="5"/>
@@ -3824,30 +3853,30 @@
       <c r="AIG9" s="3"/>
     </row>
     <row r="10" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="24"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="51"/>
-      <c r="M10" s="51"/>
-      <c r="N10" s="51"/>
-      <c r="O10" s="51"/>
-      <c r="P10" s="56"/>
-      <c r="Q10" s="52"/>
-      <c r="R10" s="53"/>
-      <c r="S10" s="53"/>
-      <c r="T10" s="54"/>
-      <c r="U10" s="54"/>
-      <c r="V10" s="54"/>
-      <c r="W10" s="54"/>
-      <c r="X10" s="55"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="75"/>
+      <c r="M10" s="75"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="48"/>
+      <c r="Q10" s="44"/>
+      <c r="R10" s="45"/>
+      <c r="S10" s="45"/>
+      <c r="T10" s="46"/>
+      <c r="U10" s="46"/>
+      <c r="V10" s="46"/>
+      <c r="W10" s="46"/>
+      <c r="X10" s="47"/>
       <c r="Y10" s="4"/>
       <c r="Z10" s="5"/>
       <c r="AA10" s="5"/>
@@ -4742,30 +4771,30 @@
       <c r="AIF10" s="5"/>
     </row>
     <row r="11" spans="1:917" s="6" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="24"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="51"/>
-      <c r="N11" s="51"/>
-      <c r="O11" s="51"/>
-      <c r="P11" s="56"/>
-      <c r="Q11" s="52"/>
-      <c r="R11" s="53"/>
-      <c r="S11" s="53"/>
-      <c r="T11" s="54"/>
-      <c r="U11" s="54"/>
-      <c r="V11" s="54"/>
-      <c r="W11" s="54"/>
-      <c r="X11" s="55"/>
+      <c r="A11" s="22"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="75"/>
+      <c r="M11" s="75"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="43"/>
+      <c r="P11" s="48"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="45"/>
+      <c r="S11" s="45"/>
+      <c r="T11" s="46"/>
+      <c r="U11" s="46"/>
+      <c r="V11" s="46"/>
+      <c r="W11" s="46"/>
+      <c r="X11" s="47"/>
       <c r="Y11" s="4"/>
       <c r="Z11" s="5"/>
       <c r="AA11" s="5"/>
@@ -5661,30 +5690,30 @@
       <c r="AIG11" s="3"/>
     </row>
     <row r="12" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="24"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="51"/>
-      <c r="M12" s="51"/>
-      <c r="N12" s="51"/>
-      <c r="O12" s="51"/>
-      <c r="P12" s="56"/>
-      <c r="Q12" s="52"/>
-      <c r="R12" s="53"/>
-      <c r="S12" s="53"/>
-      <c r="T12" s="54"/>
-      <c r="U12" s="54"/>
-      <c r="V12" s="54"/>
-      <c r="W12" s="54"/>
-      <c r="X12" s="55"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="75"/>
+      <c r="M12" s="75"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="45"/>
+      <c r="S12" s="45"/>
+      <c r="T12" s="46"/>
+      <c r="U12" s="46"/>
+      <c r="V12" s="46"/>
+      <c r="W12" s="46"/>
+      <c r="X12" s="47"/>
       <c r="Y12" s="4"/>
       <c r="Z12" s="5"/>
       <c r="AA12" s="5"/>
@@ -6579,108 +6608,108 @@
       <c r="AIF12" s="5"/>
     </row>
     <row r="13" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="51"/>
-      <c r="M13" s="51"/>
-      <c r="N13" s="51"/>
-      <c r="O13" s="51"/>
-      <c r="P13" s="56"/>
-      <c r="Q13" s="52"/>
-      <c r="R13" s="53"/>
-      <c r="S13" s="53"/>
-      <c r="T13" s="54"/>
-      <c r="U13" s="54"/>
-      <c r="V13" s="54"/>
-      <c r="W13" s="54"/>
-      <c r="X13" s="55"/>
+      <c r="A13" s="22"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="75"/>
+      <c r="M13" s="75"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="44"/>
+      <c r="R13" s="45"/>
+      <c r="S13" s="45"/>
+      <c r="T13" s="46"/>
+      <c r="U13" s="46"/>
+      <c r="V13" s="46"/>
+      <c r="W13" s="46"/>
+      <c r="X13" s="47"/>
     </row>
     <row r="14" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="24"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="51"/>
-      <c r="M14" s="51"/>
-      <c r="N14" s="51"/>
-      <c r="O14" s="51"/>
-      <c r="P14" s="56"/>
-      <c r="Q14" s="52"/>
-      <c r="R14" s="53"/>
-      <c r="S14" s="53"/>
-      <c r="T14" s="54"/>
-      <c r="U14" s="54"/>
-      <c r="V14" s="54"/>
-      <c r="W14" s="54"/>
-      <c r="X14" s="55"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="75"/>
+      <c r="M14" s="75"/>
+      <c r="N14" s="43"/>
+      <c r="O14" s="43"/>
+      <c r="P14" s="48"/>
+      <c r="Q14" s="44"/>
+      <c r="R14" s="45"/>
+      <c r="S14" s="45"/>
+      <c r="T14" s="46"/>
+      <c r="U14" s="46"/>
+      <c r="V14" s="46"/>
+      <c r="W14" s="46"/>
+      <c r="X14" s="47"/>
     </row>
     <row r="15" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="51"/>
-      <c r="M15" s="51"/>
-      <c r="N15" s="51"/>
-      <c r="O15" s="51"/>
-      <c r="P15" s="56"/>
-      <c r="Q15" s="52"/>
-      <c r="R15" s="53"/>
-      <c r="S15" s="53"/>
-      <c r="T15" s="54"/>
-      <c r="U15" s="54"/>
-      <c r="V15" s="54"/>
-      <c r="W15" s="54"/>
-      <c r="X15" s="55"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="75"/>
+      <c r="M15" s="75"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="44"/>
+      <c r="R15" s="45"/>
+      <c r="S15" s="45"/>
+      <c r="T15" s="46"/>
+      <c r="U15" s="46"/>
+      <c r="V15" s="46"/>
+      <c r="W15" s="46"/>
+      <c r="X15" s="47"/>
     </row>
     <row r="16" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="24"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="51"/>
-      <c r="M16" s="51"/>
-      <c r="N16" s="51"/>
-      <c r="O16" s="51"/>
-      <c r="P16" s="56"/>
-      <c r="Q16" s="52"/>
-      <c r="R16" s="53"/>
-      <c r="S16" s="53"/>
-      <c r="T16" s="54"/>
-      <c r="U16" s="54"/>
-      <c r="V16" s="54"/>
-      <c r="W16" s="54"/>
-      <c r="X16" s="55"/>
+      <c r="A16" s="22"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="75"/>
+      <c r="M16" s="75"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="48"/>
+      <c r="Q16" s="44"/>
+      <c r="R16" s="45"/>
+      <c r="S16" s="45"/>
+      <c r="T16" s="46"/>
+      <c r="U16" s="46"/>
+      <c r="V16" s="46"/>
+      <c r="W16" s="46"/>
+      <c r="X16" s="47"/>
       <c r="Y16" s="4"/>
       <c r="Z16" s="5"/>
       <c r="AA16" s="5"/>
@@ -7575,56 +7604,56 @@
       <c r="AIF16" s="5"/>
     </row>
     <row r="17" spans="1:916" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="51"/>
-      <c r="M17" s="51"/>
-      <c r="N17" s="51"/>
-      <c r="O17" s="51"/>
-      <c r="P17" s="56"/>
-      <c r="Q17" s="52"/>
-      <c r="R17" s="53"/>
-      <c r="S17" s="53"/>
-      <c r="T17" s="54"/>
-      <c r="U17" s="54"/>
-      <c r="V17" s="54"/>
-      <c r="W17" s="54"/>
-      <c r="X17" s="55"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="75"/>
+      <c r="M17" s="75"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="43"/>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="44"/>
+      <c r="R17" s="45"/>
+      <c r="S17" s="45"/>
+      <c r="T17" s="46"/>
+      <c r="U17" s="46"/>
+      <c r="V17" s="46"/>
+      <c r="W17" s="46"/>
+      <c r="X17" s="47"/>
     </row>
     <row r="18" spans="1:916" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="51"/>
-      <c r="M18" s="51"/>
-      <c r="N18" s="51"/>
-      <c r="O18" s="51"/>
-      <c r="P18" s="56"/>
-      <c r="Q18" s="52"/>
-      <c r="R18" s="53"/>
-      <c r="S18" s="53"/>
-      <c r="T18" s="54"/>
-      <c r="U18" s="54"/>
-      <c r="V18" s="54"/>
-      <c r="W18" s="54"/>
-      <c r="X18" s="55"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="75"/>
+      <c r="M18" s="75"/>
+      <c r="N18" s="43"/>
+      <c r="O18" s="43"/>
+      <c r="P18" s="48"/>
+      <c r="Q18" s="44"/>
+      <c r="R18" s="45"/>
+      <c r="S18" s="45"/>
+      <c r="T18" s="46"/>
+      <c r="U18" s="46"/>
+      <c r="V18" s="46"/>
+      <c r="W18" s="46"/>
+      <c r="X18" s="47"/>
       <c r="Y18" s="4"/>
       <c r="Z18" s="5"/>
       <c r="AA18" s="5"/>
@@ -8519,56 +8548,56 @@
       <c r="AIF18" s="5"/>
     </row>
     <row r="19" spans="1:916" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="51"/>
-      <c r="M19" s="51"/>
-      <c r="N19" s="51"/>
-      <c r="O19" s="51"/>
-      <c r="P19" s="56"/>
-      <c r="Q19" s="52"/>
-      <c r="R19" s="53"/>
-      <c r="S19" s="53"/>
-      <c r="T19" s="54"/>
-      <c r="U19" s="54"/>
-      <c r="V19" s="54"/>
-      <c r="W19" s="54"/>
-      <c r="X19" s="55"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="75"/>
+      <c r="M19" s="75"/>
+      <c r="N19" s="43"/>
+      <c r="O19" s="43"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="44"/>
+      <c r="R19" s="45"/>
+      <c r="S19" s="45"/>
+      <c r="T19" s="46"/>
+      <c r="U19" s="46"/>
+      <c r="V19" s="46"/>
+      <c r="W19" s="46"/>
+      <c r="X19" s="47"/>
     </row>
     <row r="20" spans="1:916" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="24"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="51"/>
-      <c r="M20" s="51"/>
-      <c r="N20" s="51"/>
-      <c r="O20" s="51"/>
-      <c r="P20" s="56"/>
-      <c r="Q20" s="52"/>
-      <c r="R20" s="53"/>
-      <c r="S20" s="53"/>
-      <c r="T20" s="54"/>
-      <c r="U20" s="54"/>
-      <c r="V20" s="54"/>
-      <c r="W20" s="54"/>
-      <c r="X20" s="55"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="75"/>
+      <c r="M20" s="75"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="43"/>
+      <c r="P20" s="48"/>
+      <c r="Q20" s="44"/>
+      <c r="R20" s="45"/>
+      <c r="S20" s="45"/>
+      <c r="T20" s="46"/>
+      <c r="U20" s="46"/>
+      <c r="V20" s="46"/>
+      <c r="W20" s="46"/>
+      <c r="X20" s="47"/>
       <c r="Y20" s="4"/>
       <c r="Z20" s="5"/>
       <c r="AA20" s="5"/>
@@ -9463,56 +9492,56 @@
       <c r="AIF20" s="5"/>
     </row>
     <row r="21" spans="1:916" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="51"/>
-      <c r="M21" s="51"/>
-      <c r="N21" s="51"/>
-      <c r="O21" s="51"/>
-      <c r="P21" s="56"/>
-      <c r="Q21" s="52"/>
-      <c r="R21" s="53"/>
-      <c r="S21" s="53"/>
-      <c r="T21" s="54"/>
-      <c r="U21" s="54"/>
-      <c r="V21" s="54"/>
-      <c r="W21" s="54"/>
-      <c r="X21" s="55"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="75"/>
+      <c r="M21" s="75"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="43"/>
+      <c r="P21" s="48"/>
+      <c r="Q21" s="44"/>
+      <c r="R21" s="45"/>
+      <c r="S21" s="45"/>
+      <c r="T21" s="46"/>
+      <c r="U21" s="46"/>
+      <c r="V21" s="46"/>
+      <c r="W21" s="46"/>
+      <c r="X21" s="47"/>
     </row>
     <row r="22" spans="1:916" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="51"/>
-      <c r="M22" s="51"/>
-      <c r="N22" s="51"/>
-      <c r="O22" s="51"/>
-      <c r="P22" s="56"/>
-      <c r="Q22" s="52"/>
-      <c r="R22" s="53"/>
-      <c r="S22" s="53"/>
-      <c r="T22" s="54"/>
-      <c r="U22" s="54"/>
-      <c r="V22" s="54"/>
-      <c r="W22" s="54"/>
-      <c r="X22" s="55"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="75"/>
+      <c r="M22" s="75"/>
+      <c r="N22" s="43"/>
+      <c r="O22" s="43"/>
+      <c r="P22" s="48"/>
+      <c r="Q22" s="44"/>
+      <c r="R22" s="45"/>
+      <c r="S22" s="45"/>
+      <c r="T22" s="46"/>
+      <c r="U22" s="46"/>
+      <c r="V22" s="46"/>
+      <c r="W22" s="46"/>
+      <c r="X22" s="47"/>
       <c r="Y22" s="7"/>
       <c r="Z22" s="5"/>
       <c r="AA22" s="5"/>
@@ -10407,30 +10436,30 @@
       <c r="AIF22" s="5"/>
     </row>
     <row r="23" spans="1:916" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="51"/>
-      <c r="M23" s="51"/>
-      <c r="N23" s="51"/>
-      <c r="O23" s="51"/>
-      <c r="P23" s="56"/>
-      <c r="Q23" s="52"/>
-      <c r="R23" s="53"/>
-      <c r="S23" s="53"/>
-      <c r="T23" s="54"/>
-      <c r="U23" s="54"/>
-      <c r="V23" s="54"/>
-      <c r="W23" s="54"/>
-      <c r="X23" s="55"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="75"/>
+      <c r="M23" s="75"/>
+      <c r="N23" s="43"/>
+      <c r="O23" s="43"/>
+      <c r="P23" s="48"/>
+      <c r="Q23" s="44"/>
+      <c r="R23" s="45"/>
+      <c r="S23" s="45"/>
+      <c r="T23" s="46"/>
+      <c r="U23" s="46"/>
+      <c r="V23" s="46"/>
+      <c r="W23" s="46"/>
+      <c r="X23" s="47"/>
       <c r="Y23" s="4"/>
       <c r="Z23" s="5"/>
       <c r="AA23" s="5"/>
@@ -11325,56 +11354,56 @@
       <c r="AIF23" s="5"/>
     </row>
     <row r="24" spans="1:916" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="24"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="51"/>
-      <c r="M24" s="51"/>
-      <c r="N24" s="51"/>
-      <c r="O24" s="51"/>
-      <c r="P24" s="56"/>
-      <c r="Q24" s="52"/>
-      <c r="R24" s="53"/>
-      <c r="S24" s="53"/>
-      <c r="T24" s="54"/>
-      <c r="U24" s="54"/>
-      <c r="V24" s="54"/>
-      <c r="W24" s="54"/>
-      <c r="X24" s="55"/>
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="75"/>
+      <c r="M24" s="75"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="43"/>
+      <c r="P24" s="48"/>
+      <c r="Q24" s="44"/>
+      <c r="R24" s="45"/>
+      <c r="S24" s="45"/>
+      <c r="T24" s="46"/>
+      <c r="U24" s="46"/>
+      <c r="V24" s="46"/>
+      <c r="W24" s="46"/>
+      <c r="X24" s="47"/>
     </row>
     <row r="25" spans="1:916" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="51"/>
-      <c r="M25" s="51"/>
-      <c r="N25" s="51"/>
-      <c r="O25" s="51"/>
-      <c r="P25" s="56"/>
-      <c r="Q25" s="52"/>
-      <c r="R25" s="53"/>
-      <c r="S25" s="53"/>
-      <c r="T25" s="54"/>
-      <c r="U25" s="54"/>
-      <c r="V25" s="54"/>
-      <c r="W25" s="54"/>
-      <c r="X25" s="55"/>
+      <c r="A25" s="22"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="75"/>
+      <c r="M25" s="75"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="43"/>
+      <c r="P25" s="48"/>
+      <c r="Q25" s="44"/>
+      <c r="R25" s="45"/>
+      <c r="S25" s="45"/>
+      <c r="T25" s="46"/>
+      <c r="U25" s="46"/>
+      <c r="V25" s="46"/>
+      <c r="W25" s="46"/>
+      <c r="X25" s="47"/>
       <c r="Y25" s="4"/>
       <c r="Z25" s="5"/>
       <c r="AA25" s="5"/>
@@ -12269,56 +12298,56 @@
       <c r="AIF25" s="5"/>
     </row>
     <row r="26" spans="1:916" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="24"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="51"/>
-      <c r="M26" s="51"/>
-      <c r="N26" s="51"/>
-      <c r="O26" s="51"/>
-      <c r="P26" s="56"/>
-      <c r="Q26" s="52"/>
-      <c r="R26" s="53"/>
-      <c r="S26" s="53"/>
-      <c r="T26" s="54"/>
-      <c r="U26" s="54"/>
-      <c r="V26" s="54"/>
-      <c r="W26" s="54"/>
-      <c r="X26" s="55"/>
+      <c r="A26" s="22"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="75"/>
+      <c r="M26" s="75"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="43"/>
+      <c r="P26" s="48"/>
+      <c r="Q26" s="44"/>
+      <c r="R26" s="45"/>
+      <c r="S26" s="45"/>
+      <c r="T26" s="46"/>
+      <c r="U26" s="46"/>
+      <c r="V26" s="46"/>
+      <c r="W26" s="46"/>
+      <c r="X26" s="47"/>
     </row>
     <row r="27" spans="1:916" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="24"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="51"/>
-      <c r="M27" s="51"/>
-      <c r="N27" s="51"/>
-      <c r="O27" s="51"/>
-      <c r="P27" s="56"/>
-      <c r="Q27" s="52"/>
-      <c r="R27" s="53"/>
-      <c r="S27" s="53"/>
-      <c r="T27" s="54"/>
-      <c r="U27" s="54"/>
-      <c r="V27" s="54"/>
-      <c r="W27" s="54"/>
-      <c r="X27" s="55"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="75"/>
+      <c r="M27" s="75"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="43"/>
+      <c r="P27" s="48"/>
+      <c r="Q27" s="44"/>
+      <c r="R27" s="45"/>
+      <c r="S27" s="45"/>
+      <c r="T27" s="46"/>
+      <c r="U27" s="46"/>
+      <c r="V27" s="46"/>
+      <c r="W27" s="46"/>
+      <c r="X27" s="47"/>
       <c r="Y27" s="5"/>
       <c r="Z27" s="5"/>
       <c r="AA27" s="5"/>
@@ -13213,30 +13242,30 @@
       <c r="AIF27" s="5"/>
     </row>
     <row r="28" spans="1:916" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="24"/>
-      <c r="B28" s="24"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="51"/>
-      <c r="M28" s="51"/>
-      <c r="N28" s="51"/>
-      <c r="O28" s="51"/>
-      <c r="P28" s="56"/>
-      <c r="Q28" s="52"/>
-      <c r="R28" s="53"/>
-      <c r="S28" s="53"/>
-      <c r="T28" s="54"/>
-      <c r="U28" s="54"/>
-      <c r="V28" s="54"/>
-      <c r="W28" s="54"/>
-      <c r="X28" s="55"/>
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="75"/>
+      <c r="M28" s="75"/>
+      <c r="N28" s="43"/>
+      <c r="O28" s="43"/>
+      <c r="P28" s="48"/>
+      <c r="Q28" s="44"/>
+      <c r="R28" s="45"/>
+      <c r="S28" s="45"/>
+      <c r="T28" s="46"/>
+      <c r="U28" s="46"/>
+      <c r="V28" s="46"/>
+      <c r="W28" s="46"/>
+      <c r="X28" s="47"/>
       <c r="Y28" s="4"/>
       <c r="Z28" s="5"/>
       <c r="AA28" s="5"/>
@@ -14131,30 +14160,30 @@
       <c r="AIF28" s="5"/>
     </row>
     <row r="29" spans="1:916" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="24"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="23"/>
-      <c r="L29" s="51"/>
-      <c r="M29" s="51"/>
-      <c r="N29" s="51"/>
-      <c r="O29" s="51"/>
-      <c r="P29" s="56"/>
-      <c r="Q29" s="52"/>
-      <c r="R29" s="53"/>
-      <c r="S29" s="53"/>
-      <c r="T29" s="54"/>
-      <c r="U29" s="54"/>
-      <c r="V29" s="54"/>
-      <c r="W29" s="54"/>
-      <c r="X29" s="55"/>
+      <c r="A29" s="22"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="75"/>
+      <c r="M29" s="75"/>
+      <c r="N29" s="43"/>
+      <c r="O29" s="43"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="44"/>
+      <c r="R29" s="45"/>
+      <c r="S29" s="45"/>
+      <c r="T29" s="46"/>
+      <c r="U29" s="46"/>
+      <c r="V29" s="46"/>
+      <c r="W29" s="46"/>
+      <c r="X29" s="47"/>
       <c r="Y29" s="4"/>
       <c r="Z29" s="5"/>
       <c r="AA29" s="5"/>
@@ -15049,30 +15078,30 @@
       <c r="AIF29" s="5"/>
     </row>
     <row r="30" spans="1:916" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="24"/>
-      <c r="B30" s="24"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="23"/>
-      <c r="L30" s="51"/>
-      <c r="M30" s="51"/>
-      <c r="N30" s="51"/>
-      <c r="O30" s="51"/>
-      <c r="P30" s="56"/>
-      <c r="Q30" s="52"/>
-      <c r="R30" s="53"/>
-      <c r="S30" s="53"/>
-      <c r="T30" s="54"/>
-      <c r="U30" s="54"/>
-      <c r="V30" s="54"/>
-      <c r="W30" s="54"/>
-      <c r="X30" s="55"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="75"/>
+      <c r="M30" s="75"/>
+      <c r="N30" s="43"/>
+      <c r="O30" s="43"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="44"/>
+      <c r="R30" s="45"/>
+      <c r="S30" s="45"/>
+      <c r="T30" s="46"/>
+      <c r="U30" s="46"/>
+      <c r="V30" s="46"/>
+      <c r="W30" s="46"/>
+      <c r="X30" s="47"/>
       <c r="Y30" s="4"/>
       <c r="Z30" s="5"/>
       <c r="AA30" s="5"/>
@@ -15967,30 +15996,30 @@
       <c r="AIF30" s="5"/>
     </row>
     <row r="31" spans="1:916" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="24"/>
-      <c r="B31" s="24"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="51"/>
-      <c r="M31" s="51"/>
-      <c r="N31" s="51"/>
-      <c r="O31" s="51"/>
-      <c r="P31" s="56"/>
-      <c r="Q31" s="52"/>
-      <c r="R31" s="53"/>
-      <c r="S31" s="53"/>
-      <c r="T31" s="54"/>
-      <c r="U31" s="54"/>
-      <c r="V31" s="54"/>
-      <c r="W31" s="54"/>
-      <c r="X31" s="55"/>
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="65"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="75"/>
+      <c r="M31" s="75"/>
+      <c r="N31" s="43"/>
+      <c r="O31" s="43"/>
+      <c r="P31" s="48"/>
+      <c r="Q31" s="44"/>
+      <c r="R31" s="45"/>
+      <c r="S31" s="45"/>
+      <c r="T31" s="46"/>
+      <c r="U31" s="46"/>
+      <c r="V31" s="46"/>
+      <c r="W31" s="46"/>
+      <c r="X31" s="47"/>
       <c r="Y31" s="4"/>
       <c r="Z31" s="5"/>
       <c r="AA31" s="5"/>
@@ -16885,30 +16914,30 @@
       <c r="AIF31" s="5"/>
     </row>
     <row r="32" spans="1:916" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="24"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="23"/>
-      <c r="L32" s="51"/>
-      <c r="M32" s="51"/>
-      <c r="N32" s="51"/>
-      <c r="O32" s="51"/>
-      <c r="P32" s="56"/>
-      <c r="Q32" s="52"/>
-      <c r="R32" s="53"/>
-      <c r="S32" s="53"/>
-      <c r="T32" s="54"/>
-      <c r="U32" s="54"/>
-      <c r="V32" s="54"/>
-      <c r="W32" s="54"/>
-      <c r="X32" s="55"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="65"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="75"/>
+      <c r="M32" s="75"/>
+      <c r="N32" s="43"/>
+      <c r="O32" s="43"/>
+      <c r="P32" s="48"/>
+      <c r="Q32" s="44"/>
+      <c r="R32" s="45"/>
+      <c r="S32" s="45"/>
+      <c r="T32" s="46"/>
+      <c r="U32" s="46"/>
+      <c r="V32" s="46"/>
+      <c r="W32" s="46"/>
+      <c r="X32" s="47"/>
       <c r="Y32" s="4"/>
       <c r="Z32" s="5"/>
       <c r="AA32" s="5"/>
@@ -17803,56 +17832,56 @@
       <c r="AIF32" s="5"/>
     </row>
     <row r="33" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="22"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="51"/>
-      <c r="M33" s="51"/>
-      <c r="N33" s="51"/>
-      <c r="O33" s="51"/>
-      <c r="P33" s="56"/>
-      <c r="Q33" s="52"/>
-      <c r="R33" s="53"/>
-      <c r="S33" s="53"/>
-      <c r="T33" s="54"/>
-      <c r="U33" s="54"/>
-      <c r="V33" s="54"/>
-      <c r="W33" s="54"/>
-      <c r="X33" s="55"/>
+      <c r="A33" s="13"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="65"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="75"/>
+      <c r="M33" s="75"/>
+      <c r="N33" s="43"/>
+      <c r="O33" s="43"/>
+      <c r="P33" s="48"/>
+      <c r="Q33" s="44"/>
+      <c r="R33" s="45"/>
+      <c r="S33" s="45"/>
+      <c r="T33" s="46"/>
+      <c r="U33" s="46"/>
+      <c r="V33" s="46"/>
+      <c r="W33" s="46"/>
+      <c r="X33" s="47"/>
     </row>
     <row r="34" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24"/>
-      <c r="B34" s="24"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="21"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="23"/>
-      <c r="L34" s="51"/>
-      <c r="M34" s="51"/>
-      <c r="N34" s="51"/>
-      <c r="O34" s="51"/>
-      <c r="P34" s="56"/>
-      <c r="Q34" s="52"/>
-      <c r="R34" s="53"/>
-      <c r="S34" s="53"/>
-      <c r="T34" s="54"/>
-      <c r="U34" s="54"/>
-      <c r="V34" s="54"/>
-      <c r="W34" s="54"/>
-      <c r="X34" s="55"/>
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="65"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="21"/>
+      <c r="L34" s="75"/>
+      <c r="M34" s="75"/>
+      <c r="N34" s="43"/>
+      <c r="O34" s="43"/>
+      <c r="P34" s="48"/>
+      <c r="Q34" s="44"/>
+      <c r="R34" s="45"/>
+      <c r="S34" s="45"/>
+      <c r="T34" s="46"/>
+      <c r="U34" s="46"/>
+      <c r="V34" s="46"/>
+      <c r="W34" s="46"/>
+      <c r="X34" s="47"/>
       <c r="Y34" s="5"/>
       <c r="Z34" s="5"/>
       <c r="AA34" s="5"/>
@@ -18747,30 +18776,30 @@
       <c r="AIF34" s="5"/>
     </row>
     <row r="35" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="24"/>
-      <c r="B35" s="24"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="22"/>
-      <c r="K35" s="23"/>
-      <c r="L35" s="51"/>
-      <c r="M35" s="51"/>
-      <c r="N35" s="51"/>
-      <c r="O35" s="51"/>
-      <c r="P35" s="56"/>
-      <c r="Q35" s="52"/>
-      <c r="R35" s="53"/>
-      <c r="S35" s="53"/>
-      <c r="T35" s="54"/>
-      <c r="U35" s="54"/>
-      <c r="V35" s="54"/>
-      <c r="W35" s="54"/>
-      <c r="X35" s="55"/>
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="75"/>
+      <c r="M35" s="75"/>
+      <c r="N35" s="43"/>
+      <c r="O35" s="43"/>
+      <c r="P35" s="48"/>
+      <c r="Q35" s="44"/>
+      <c r="R35" s="45"/>
+      <c r="S35" s="45"/>
+      <c r="T35" s="46"/>
+      <c r="U35" s="46"/>
+      <c r="V35" s="46"/>
+      <c r="W35" s="46"/>
+      <c r="X35" s="47"/>
       <c r="Y35" s="4"/>
       <c r="Z35" s="5"/>
       <c r="AA35" s="5"/>
@@ -19665,30 +19694,30 @@
       <c r="AIF35" s="5"/>
     </row>
     <row r="36" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24"/>
-      <c r="B36" s="24"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="22"/>
-      <c r="K36" s="23"/>
-      <c r="L36" s="51"/>
-      <c r="M36" s="51"/>
-      <c r="N36" s="51"/>
-      <c r="O36" s="51"/>
-      <c r="P36" s="56"/>
-      <c r="Q36" s="52"/>
-      <c r="R36" s="53"/>
-      <c r="S36" s="53"/>
-      <c r="T36" s="54"/>
-      <c r="U36" s="54"/>
-      <c r="V36" s="54"/>
-      <c r="W36" s="54"/>
-      <c r="X36" s="55"/>
+      <c r="A36" s="22"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="65"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="20"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="75"/>
+      <c r="M36" s="75"/>
+      <c r="N36" s="43"/>
+      <c r="O36" s="43"/>
+      <c r="P36" s="48"/>
+      <c r="Q36" s="44"/>
+      <c r="R36" s="45"/>
+      <c r="S36" s="45"/>
+      <c r="T36" s="46"/>
+      <c r="U36" s="46"/>
+      <c r="V36" s="46"/>
+      <c r="W36" s="46"/>
+      <c r="X36" s="47"/>
       <c r="Y36" s="4"/>
       <c r="Z36" s="5"/>
       <c r="AA36" s="5"/>
@@ -20583,30 +20612,30 @@
       <c r="AIF36" s="5"/>
     </row>
     <row r="37" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="24"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="21"/>
-      <c r="J37" s="22"/>
-      <c r="K37" s="23"/>
-      <c r="L37" s="51"/>
-      <c r="M37" s="51"/>
-      <c r="N37" s="51"/>
-      <c r="O37" s="51"/>
-      <c r="P37" s="56"/>
-      <c r="Q37" s="52"/>
-      <c r="R37" s="53"/>
-      <c r="S37" s="53"/>
-      <c r="T37" s="54"/>
-      <c r="U37" s="54"/>
-      <c r="V37" s="54"/>
-      <c r="W37" s="54"/>
-      <c r="X37" s="55"/>
+      <c r="A37" s="22"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="65"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="21"/>
+      <c r="L37" s="75"/>
+      <c r="M37" s="75"/>
+      <c r="N37" s="43"/>
+      <c r="O37" s="43"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="44"/>
+      <c r="R37" s="45"/>
+      <c r="S37" s="45"/>
+      <c r="T37" s="46"/>
+      <c r="U37" s="46"/>
+      <c r="V37" s="46"/>
+      <c r="W37" s="46"/>
+      <c r="X37" s="47"/>
       <c r="Y37" s="4"/>
       <c r="Z37" s="5"/>
       <c r="AA37" s="5"/>
@@ -21501,30 +21530,30 @@
       <c r="AIF37" s="5"/>
     </row>
     <row r="38" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="14"/>
-      <c r="B38" s="24"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="21"/>
-      <c r="J38" s="22"/>
-      <c r="K38" s="23"/>
-      <c r="L38" s="51"/>
-      <c r="M38" s="51"/>
-      <c r="N38" s="51"/>
-      <c r="O38" s="51"/>
-      <c r="P38" s="56"/>
-      <c r="Q38" s="52"/>
-      <c r="R38" s="53"/>
-      <c r="S38" s="53"/>
-      <c r="T38" s="54"/>
-      <c r="U38" s="54"/>
-      <c r="V38" s="54"/>
-      <c r="W38" s="54"/>
-      <c r="X38" s="55"/>
+      <c r="A38" s="13"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="21"/>
+      <c r="L38" s="75"/>
+      <c r="M38" s="75"/>
+      <c r="N38" s="43"/>
+      <c r="O38" s="43"/>
+      <c r="P38" s="48"/>
+      <c r="Q38" s="44"/>
+      <c r="R38" s="45"/>
+      <c r="S38" s="45"/>
+      <c r="T38" s="46"/>
+      <c r="U38" s="46"/>
+      <c r="V38" s="46"/>
+      <c r="W38" s="46"/>
+      <c r="X38" s="47"/>
       <c r="Y38" s="5"/>
       <c r="Z38" s="5"/>
       <c r="AA38" s="5"/>
@@ -22419,30 +22448,30 @@
       <c r="AIF38" s="5"/>
     </row>
     <row r="39" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="22"/>
-      <c r="K39" s="23"/>
-      <c r="L39" s="51"/>
-      <c r="M39" s="51"/>
-      <c r="N39" s="51"/>
-      <c r="O39" s="51"/>
-      <c r="P39" s="56"/>
-      <c r="Q39" s="52"/>
-      <c r="R39" s="53"/>
-      <c r="S39" s="53"/>
-      <c r="T39" s="54"/>
-      <c r="U39" s="54"/>
-      <c r="V39" s="54"/>
-      <c r="W39" s="54"/>
-      <c r="X39" s="55"/>
+      <c r="A39" s="22"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="65"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="20"/>
+      <c r="K39" s="21"/>
+      <c r="L39" s="75"/>
+      <c r="M39" s="75"/>
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="48"/>
+      <c r="Q39" s="44"/>
+      <c r="R39" s="45"/>
+      <c r="S39" s="45"/>
+      <c r="T39" s="46"/>
+      <c r="U39" s="46"/>
+      <c r="V39" s="46"/>
+      <c r="W39" s="46"/>
+      <c r="X39" s="47"/>
       <c r="Y39" s="4"/>
       <c r="Z39" s="5"/>
       <c r="AA39" s="5"/>
@@ -23337,30 +23366,30 @@
       <c r="AIF39" s="5"/>
     </row>
     <row r="40" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="22"/>
-      <c r="K40" s="23"/>
-      <c r="L40" s="51"/>
-      <c r="M40" s="51"/>
-      <c r="N40" s="51"/>
-      <c r="O40" s="51"/>
-      <c r="P40" s="56"/>
-      <c r="Q40" s="52"/>
-      <c r="R40" s="53"/>
-      <c r="S40" s="53"/>
-      <c r="T40" s="54"/>
-      <c r="U40" s="54"/>
-      <c r="V40" s="54"/>
-      <c r="W40" s="54"/>
-      <c r="X40" s="55"/>
+      <c r="A40" s="22"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="65"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="20"/>
+      <c r="K40" s="21"/>
+      <c r="L40" s="75"/>
+      <c r="M40" s="75"/>
+      <c r="N40" s="43"/>
+      <c r="O40" s="43"/>
+      <c r="P40" s="48"/>
+      <c r="Q40" s="44"/>
+      <c r="R40" s="45"/>
+      <c r="S40" s="45"/>
+      <c r="T40" s="46"/>
+      <c r="U40" s="46"/>
+      <c r="V40" s="46"/>
+      <c r="W40" s="46"/>
+      <c r="X40" s="47"/>
       <c r="Y40" s="4"/>
       <c r="Z40" s="5"/>
       <c r="AA40" s="5"/>
@@ -24255,30 +24284,30 @@
       <c r="AIF40" s="5"/>
     </row>
     <row r="41" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="14"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="23"/>
-      <c r="L41" s="51"/>
-      <c r="M41" s="51"/>
-      <c r="N41" s="51"/>
-      <c r="O41" s="51"/>
-      <c r="P41" s="56"/>
-      <c r="Q41" s="52"/>
-      <c r="R41" s="53"/>
-      <c r="S41" s="53"/>
-      <c r="T41" s="54"/>
-      <c r="U41" s="54"/>
-      <c r="V41" s="54"/>
-      <c r="W41" s="54"/>
-      <c r="X41" s="55"/>
+      <c r="A41" s="13"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="65"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="21"/>
+      <c r="L41" s="75"/>
+      <c r="M41" s="75"/>
+      <c r="N41" s="43"/>
+      <c r="O41" s="43"/>
+      <c r="P41" s="48"/>
+      <c r="Q41" s="44"/>
+      <c r="R41" s="45"/>
+      <c r="S41" s="45"/>
+      <c r="T41" s="46"/>
+      <c r="U41" s="46"/>
+      <c r="V41" s="46"/>
+      <c r="W41" s="46"/>
+      <c r="X41" s="47"/>
       <c r="Y41" s="4"/>
       <c r="Z41" s="5"/>
       <c r="AA41" s="5"/>
@@ -25173,30 +25202,30 @@
       <c r="AIF41" s="5"/>
     </row>
     <row r="42" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="14"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="21"/>
-      <c r="J42" s="22"/>
-      <c r="K42" s="23"/>
-      <c r="L42" s="51"/>
-      <c r="M42" s="51"/>
-      <c r="N42" s="51"/>
-      <c r="O42" s="51"/>
-      <c r="P42" s="56"/>
-      <c r="Q42" s="52"/>
-      <c r="R42" s="53"/>
-      <c r="S42" s="53"/>
-      <c r="T42" s="54"/>
-      <c r="U42" s="54"/>
-      <c r="V42" s="54"/>
-      <c r="W42" s="54"/>
-      <c r="X42" s="55"/>
+      <c r="A42" s="13"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="20"/>
+      <c r="K42" s="21"/>
+      <c r="L42" s="75"/>
+      <c r="M42" s="75"/>
+      <c r="N42" s="43"/>
+      <c r="O42" s="43"/>
+      <c r="P42" s="48"/>
+      <c r="Q42" s="44"/>
+      <c r="R42" s="45"/>
+      <c r="S42" s="45"/>
+      <c r="T42" s="46"/>
+      <c r="U42" s="46"/>
+      <c r="V42" s="46"/>
+      <c r="W42" s="46"/>
+      <c r="X42" s="47"/>
       <c r="Y42" s="4"/>
       <c r="Z42" s="5"/>
       <c r="AA42" s="5"/>
@@ -26091,56 +26120,56 @@
       <c r="AIF42" s="5"/>
     </row>
     <row r="43" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="24"/>
-      <c r="B43" s="24"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="21"/>
-      <c r="J43" s="22"/>
-      <c r="K43" s="23"/>
-      <c r="L43" s="51"/>
-      <c r="M43" s="51"/>
-      <c r="N43" s="51"/>
-      <c r="O43" s="51"/>
-      <c r="P43" s="56"/>
-      <c r="Q43" s="52"/>
-      <c r="R43" s="53"/>
-      <c r="S43" s="53"/>
-      <c r="T43" s="54"/>
-      <c r="U43" s="54"/>
-      <c r="V43" s="54"/>
-      <c r="W43" s="54"/>
-      <c r="X43" s="55"/>
+      <c r="A43" s="22"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="20"/>
+      <c r="K43" s="21"/>
+      <c r="L43" s="75"/>
+      <c r="M43" s="75"/>
+      <c r="N43" s="43"/>
+      <c r="O43" s="43"/>
+      <c r="P43" s="48"/>
+      <c r="Q43" s="44"/>
+      <c r="R43" s="45"/>
+      <c r="S43" s="45"/>
+      <c r="T43" s="46"/>
+      <c r="U43" s="46"/>
+      <c r="V43" s="46"/>
+      <c r="W43" s="46"/>
+      <c r="X43" s="47"/>
     </row>
     <row r="44" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24"/>
-      <c r="B44" s="24"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="21"/>
-      <c r="J44" s="22"/>
-      <c r="K44" s="23"/>
-      <c r="L44" s="51"/>
-      <c r="M44" s="51"/>
-      <c r="N44" s="51"/>
-      <c r="O44" s="51"/>
-      <c r="P44" s="56"/>
-      <c r="Q44" s="52"/>
-      <c r="R44" s="53"/>
-      <c r="S44" s="53"/>
-      <c r="T44" s="54"/>
-      <c r="U44" s="54"/>
-      <c r="V44" s="54"/>
-      <c r="W44" s="54"/>
-      <c r="X44" s="55"/>
+      <c r="A44" s="22"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="65"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="21"/>
+      <c r="L44" s="75"/>
+      <c r="M44" s="75"/>
+      <c r="N44" s="43"/>
+      <c r="O44" s="43"/>
+      <c r="P44" s="48"/>
+      <c r="Q44" s="44"/>
+      <c r="R44" s="45"/>
+      <c r="S44" s="45"/>
+      <c r="T44" s="46"/>
+      <c r="U44" s="46"/>
+      <c r="V44" s="46"/>
+      <c r="W44" s="46"/>
+      <c r="X44" s="47"/>
       <c r="Y44" s="4"/>
       <c r="Z44" s="5"/>
       <c r="AA44" s="5"/>
@@ -27035,30 +27064,30 @@
       <c r="AIF44" s="5"/>
     </row>
     <row r="45" spans="1:917" s="6" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="24"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="21"/>
-      <c r="J45" s="22"/>
-      <c r="K45" s="23"/>
-      <c r="L45" s="51"/>
-      <c r="M45" s="51"/>
-      <c r="N45" s="51"/>
-      <c r="O45" s="51"/>
-      <c r="P45" s="56"/>
-      <c r="Q45" s="52"/>
-      <c r="R45" s="53"/>
-      <c r="S45" s="53"/>
-      <c r="T45" s="54"/>
-      <c r="U45" s="54"/>
-      <c r="V45" s="54"/>
-      <c r="W45" s="54"/>
-      <c r="X45" s="55"/>
+      <c r="A45" s="22"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="65"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="21"/>
+      <c r="L45" s="75"/>
+      <c r="M45" s="75"/>
+      <c r="N45" s="43"/>
+      <c r="O45" s="43"/>
+      <c r="P45" s="48"/>
+      <c r="Q45" s="44"/>
+      <c r="R45" s="45"/>
+      <c r="S45" s="45"/>
+      <c r="T45" s="46"/>
+      <c r="U45" s="46"/>
+      <c r="V45" s="46"/>
+      <c r="W45" s="46"/>
+      <c r="X45" s="47"/>
       <c r="Y45" s="4"/>
       <c r="Z45" s="5"/>
       <c r="AA45" s="5"/>
@@ -27954,30 +27983,30 @@
       <c r="AIG45" s="3"/>
     </row>
     <row r="46" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="14"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="15"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="20"/>
-      <c r="I46" s="21"/>
-      <c r="J46" s="22"/>
-      <c r="K46" s="23"/>
-      <c r="L46" s="51"/>
-      <c r="M46" s="51"/>
-      <c r="N46" s="51"/>
-      <c r="O46" s="51"/>
-      <c r="P46" s="56"/>
-      <c r="Q46" s="52"/>
-      <c r="R46" s="53"/>
-      <c r="S46" s="53"/>
-      <c r="T46" s="54"/>
-      <c r="U46" s="54"/>
-      <c r="V46" s="54"/>
-      <c r="W46" s="54"/>
-      <c r="X46" s="55"/>
+      <c r="A46" s="13"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="65"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="20"/>
+      <c r="K46" s="21"/>
+      <c r="L46" s="75"/>
+      <c r="M46" s="75"/>
+      <c r="N46" s="43"/>
+      <c r="O46" s="43"/>
+      <c r="P46" s="48"/>
+      <c r="Q46" s="44"/>
+      <c r="R46" s="45"/>
+      <c r="S46" s="45"/>
+      <c r="T46" s="46"/>
+      <c r="U46" s="46"/>
+      <c r="V46" s="46"/>
+      <c r="W46" s="46"/>
+      <c r="X46" s="47"/>
       <c r="Y46" s="4"/>
       <c r="Z46" s="5"/>
       <c r="AA46" s="5"/>
@@ -28872,82 +28901,82 @@
       <c r="AIF46" s="5"/>
     </row>
     <row r="47" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="24"/>
-      <c r="B47" s="24"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="21"/>
-      <c r="J47" s="22"/>
-      <c r="K47" s="23"/>
-      <c r="L47" s="51"/>
-      <c r="M47" s="51"/>
-      <c r="N47" s="51"/>
-      <c r="O47" s="51"/>
-      <c r="P47" s="56"/>
-      <c r="Q47" s="52"/>
-      <c r="R47" s="53"/>
-      <c r="S47" s="53"/>
-      <c r="T47" s="54"/>
-      <c r="U47" s="54"/>
-      <c r="V47" s="54"/>
-      <c r="W47" s="54"/>
-      <c r="X47" s="55"/>
+      <c r="A47" s="22"/>
+      <c r="B47" s="22"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="19"/>
+      <c r="J47" s="20"/>
+      <c r="K47" s="21"/>
+      <c r="L47" s="75"/>
+      <c r="M47" s="75"/>
+      <c r="N47" s="43"/>
+      <c r="O47" s="43"/>
+      <c r="P47" s="48"/>
+      <c r="Q47" s="44"/>
+      <c r="R47" s="45"/>
+      <c r="S47" s="45"/>
+      <c r="T47" s="46"/>
+      <c r="U47" s="46"/>
+      <c r="V47" s="46"/>
+      <c r="W47" s="46"/>
+      <c r="X47" s="47"/>
     </row>
     <row r="48" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="24"/>
-      <c r="B48" s="25"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="20"/>
-      <c r="I48" s="21"/>
-      <c r="J48" s="22"/>
-      <c r="K48" s="23"/>
-      <c r="L48" s="51"/>
-      <c r="M48" s="51"/>
-      <c r="N48" s="51"/>
-      <c r="O48" s="51"/>
-      <c r="P48" s="56"/>
-      <c r="Q48" s="52"/>
-      <c r="R48" s="53"/>
-      <c r="S48" s="53"/>
-      <c r="T48" s="54"/>
-      <c r="U48" s="54"/>
-      <c r="V48" s="54"/>
-      <c r="W48" s="54"/>
-      <c r="X48" s="55"/>
+      <c r="A48" s="22"/>
+      <c r="B48" s="23"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="65"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="19"/>
+      <c r="J48" s="20"/>
+      <c r="K48" s="21"/>
+      <c r="L48" s="75"/>
+      <c r="M48" s="75"/>
+      <c r="N48" s="43"/>
+      <c r="O48" s="43"/>
+      <c r="P48" s="48"/>
+      <c r="Q48" s="44"/>
+      <c r="R48" s="45"/>
+      <c r="S48" s="45"/>
+      <c r="T48" s="46"/>
+      <c r="U48" s="46"/>
+      <c r="V48" s="46"/>
+      <c r="W48" s="46"/>
+      <c r="X48" s="47"/>
     </row>
     <row r="49" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="24"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="20"/>
-      <c r="I49" s="21"/>
-      <c r="J49" s="22"/>
-      <c r="K49" s="23"/>
-      <c r="L49" s="51"/>
-      <c r="M49" s="51"/>
-      <c r="N49" s="51"/>
-      <c r="O49" s="51"/>
-      <c r="P49" s="56"/>
-      <c r="Q49" s="52"/>
-      <c r="R49" s="53"/>
-      <c r="S49" s="53"/>
-      <c r="T49" s="54"/>
-      <c r="U49" s="54"/>
-      <c r="V49" s="54"/>
-      <c r="W49" s="54"/>
-      <c r="X49" s="55"/>
+      <c r="A49" s="22"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="65"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="19"/>
+      <c r="J49" s="20"/>
+      <c r="K49" s="21"/>
+      <c r="L49" s="75"/>
+      <c r="M49" s="75"/>
+      <c r="N49" s="43"/>
+      <c r="O49" s="43"/>
+      <c r="P49" s="48"/>
+      <c r="Q49" s="44"/>
+      <c r="R49" s="45"/>
+      <c r="S49" s="45"/>
+      <c r="T49" s="46"/>
+      <c r="U49" s="46"/>
+      <c r="V49" s="46"/>
+      <c r="W49" s="46"/>
+      <c r="X49" s="47"/>
       <c r="Y49" s="4"/>
       <c r="Z49" s="5"/>
       <c r="AA49" s="5"/>
@@ -29842,30 +29871,30 @@
       <c r="AIF49" s="5"/>
     </row>
     <row r="50" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="14"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="21"/>
-      <c r="J50" s="22"/>
-      <c r="K50" s="23"/>
-      <c r="L50" s="51"/>
-      <c r="M50" s="51"/>
-      <c r="N50" s="51"/>
-      <c r="O50" s="51"/>
-      <c r="P50" s="56"/>
-      <c r="Q50" s="52"/>
-      <c r="R50" s="53"/>
-      <c r="S50" s="53"/>
-      <c r="T50" s="54"/>
-      <c r="U50" s="54"/>
-      <c r="V50" s="54"/>
-      <c r="W50" s="54"/>
-      <c r="X50" s="55"/>
+      <c r="A50" s="13"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="65"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="19"/>
+      <c r="J50" s="20"/>
+      <c r="K50" s="21"/>
+      <c r="L50" s="75"/>
+      <c r="M50" s="75"/>
+      <c r="N50" s="43"/>
+      <c r="O50" s="43"/>
+      <c r="P50" s="48"/>
+      <c r="Q50" s="44"/>
+      <c r="R50" s="45"/>
+      <c r="S50" s="45"/>
+      <c r="T50" s="46"/>
+      <c r="U50" s="46"/>
+      <c r="V50" s="46"/>
+      <c r="W50" s="46"/>
+      <c r="X50" s="47"/>
       <c r="Y50" s="4"/>
       <c r="Z50" s="5"/>
       <c r="AA50" s="5"/>
@@ -30760,108 +30789,108 @@
       <c r="AIF50" s="5"/>
     </row>
     <row r="51" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="26"/>
-      <c r="B51" s="26"/>
-      <c r="C51" s="27"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="29"/>
-      <c r="G51" s="20"/>
-      <c r="H51" s="20"/>
-      <c r="I51" s="30"/>
-      <c r="J51" s="31"/>
-      <c r="K51" s="23"/>
-      <c r="L51" s="51"/>
-      <c r="M51" s="51"/>
-      <c r="N51" s="51"/>
-      <c r="O51" s="51"/>
-      <c r="P51" s="56"/>
-      <c r="Q51" s="52"/>
-      <c r="R51" s="53"/>
-      <c r="S51" s="53"/>
-      <c r="T51" s="54"/>
-      <c r="U51" s="54"/>
-      <c r="V51" s="54"/>
-      <c r="W51" s="54"/>
-      <c r="X51" s="55"/>
+      <c r="A51" s="24"/>
+      <c r="B51" s="24"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="66"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="27"/>
+      <c r="J51" s="28"/>
+      <c r="K51" s="21"/>
+      <c r="L51" s="75"/>
+      <c r="M51" s="75"/>
+      <c r="N51" s="43"/>
+      <c r="O51" s="43"/>
+      <c r="P51" s="48"/>
+      <c r="Q51" s="44"/>
+      <c r="R51" s="45"/>
+      <c r="S51" s="45"/>
+      <c r="T51" s="46"/>
+      <c r="U51" s="46"/>
+      <c r="V51" s="46"/>
+      <c r="W51" s="46"/>
+      <c r="X51" s="47"/>
     </row>
     <row r="52" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="26"/>
-      <c r="B52" s="26"/>
-      <c r="C52" s="32"/>
-      <c r="D52" s="32"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="20"/>
-      <c r="I52" s="33"/>
-      <c r="J52" s="34"/>
-      <c r="K52" s="23"/>
-      <c r="L52" s="51"/>
-      <c r="M52" s="51"/>
-      <c r="N52" s="51"/>
-      <c r="O52" s="51"/>
-      <c r="P52" s="56"/>
-      <c r="Q52" s="52"/>
-      <c r="R52" s="53"/>
-      <c r="S52" s="53"/>
-      <c r="T52" s="54"/>
-      <c r="U52" s="54"/>
-      <c r="V52" s="54"/>
-      <c r="W52" s="54"/>
-      <c r="X52" s="55"/>
+      <c r="A52" s="24"/>
+      <c r="B52" s="24"/>
+      <c r="C52" s="61"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="66"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="71"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="21"/>
+      <c r="L52" s="75"/>
+      <c r="M52" s="75"/>
+      <c r="N52" s="43"/>
+      <c r="O52" s="43"/>
+      <c r="P52" s="48"/>
+      <c r="Q52" s="44"/>
+      <c r="R52" s="45"/>
+      <c r="S52" s="45"/>
+      <c r="T52" s="46"/>
+      <c r="U52" s="46"/>
+      <c r="V52" s="46"/>
+      <c r="W52" s="46"/>
+      <c r="X52" s="47"/>
     </row>
     <row r="53" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="35"/>
-      <c r="B53" s="35"/>
-      <c r="C53" s="36"/>
-      <c r="D53" s="36"/>
-      <c r="E53" s="17"/>
-      <c r="F53" s="37"/>
-      <c r="G53" s="37"/>
-      <c r="H53" s="20"/>
-      <c r="I53" s="38"/>
-      <c r="J53" s="38"/>
-      <c r="K53" s="23"/>
-      <c r="L53" s="51"/>
-      <c r="M53" s="51"/>
-      <c r="N53" s="51"/>
-      <c r="O53" s="51"/>
-      <c r="P53" s="56"/>
-      <c r="Q53" s="52"/>
-      <c r="R53" s="53"/>
-      <c r="S53" s="53"/>
-      <c r="T53" s="54"/>
-      <c r="U53" s="54"/>
-      <c r="V53" s="54"/>
-      <c r="W53" s="54"/>
-      <c r="X53" s="55"/>
+      <c r="A53" s="31"/>
+      <c r="B53" s="31"/>
+      <c r="C53" s="25"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="67"/>
+      <c r="G53" s="33"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="27"/>
+      <c r="J53" s="34"/>
+      <c r="K53" s="21"/>
+      <c r="L53" s="75"/>
+      <c r="M53" s="75"/>
+      <c r="N53" s="43"/>
+      <c r="O53" s="43"/>
+      <c r="P53" s="48"/>
+      <c r="Q53" s="44"/>
+      <c r="R53" s="45"/>
+      <c r="S53" s="45"/>
+      <c r="T53" s="46"/>
+      <c r="U53" s="46"/>
+      <c r="V53" s="46"/>
+      <c r="W53" s="46"/>
+      <c r="X53" s="47"/>
     </row>
     <row r="54" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="35"/>
-      <c r="B54" s="35"/>
-      <c r="C54" s="36"/>
-      <c r="D54" s="36"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="39"/>
-      <c r="G54" s="39"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="38"/>
-      <c r="J54" s="38"/>
-      <c r="K54" s="23"/>
-      <c r="L54" s="51"/>
-      <c r="M54" s="51"/>
-      <c r="N54" s="51"/>
-      <c r="O54" s="51"/>
-      <c r="P54" s="56"/>
-      <c r="Q54" s="52"/>
-      <c r="R54" s="53"/>
-      <c r="S54" s="53"/>
-      <c r="T54" s="54"/>
-      <c r="U54" s="54"/>
-      <c r="V54" s="54"/>
-      <c r="W54" s="54"/>
-      <c r="X54" s="55"/>
+      <c r="A54" s="31"/>
+      <c r="B54" s="31"/>
+      <c r="C54" s="25"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="67"/>
+      <c r="G54" s="35"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="27"/>
+      <c r="J54" s="34"/>
+      <c r="K54" s="21"/>
+      <c r="L54" s="75"/>
+      <c r="M54" s="75"/>
+      <c r="N54" s="43"/>
+      <c r="O54" s="43"/>
+      <c r="P54" s="48"/>
+      <c r="Q54" s="44"/>
+      <c r="R54" s="45"/>
+      <c r="S54" s="45"/>
+      <c r="T54" s="46"/>
+      <c r="U54" s="46"/>
+      <c r="V54" s="46"/>
+      <c r="W54" s="46"/>
+      <c r="X54" s="47"/>
       <c r="Y54" s="4"/>
       <c r="Z54" s="5"/>
       <c r="AA54" s="5"/>
@@ -31756,30 +31785,30 @@
       <c r="AIF54" s="5"/>
     </row>
     <row r="55" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="35"/>
-      <c r="B55" s="24"/>
-      <c r="C55" s="36"/>
-      <c r="D55" s="36"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="37"/>
-      <c r="G55" s="37"/>
-      <c r="H55" s="20"/>
-      <c r="I55" s="38"/>
-      <c r="J55" s="38"/>
-      <c r="K55" s="23"/>
-      <c r="L55" s="51"/>
-      <c r="M55" s="51"/>
-      <c r="N55" s="51"/>
-      <c r="O55" s="51"/>
-      <c r="P55" s="56"/>
-      <c r="Q55" s="52"/>
-      <c r="R55" s="53"/>
-      <c r="S55" s="53"/>
-      <c r="T55" s="54"/>
-      <c r="U55" s="54"/>
-      <c r="V55" s="54"/>
-      <c r="W55" s="54"/>
-      <c r="X55" s="55"/>
+      <c r="A55" s="31"/>
+      <c r="B55" s="22"/>
+      <c r="C55" s="25"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="67"/>
+      <c r="G55" s="33"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="27"/>
+      <c r="J55" s="34"/>
+      <c r="K55" s="21"/>
+      <c r="L55" s="75"/>
+      <c r="M55" s="75"/>
+      <c r="N55" s="43"/>
+      <c r="O55" s="43"/>
+      <c r="P55" s="48"/>
+      <c r="Q55" s="44"/>
+      <c r="R55" s="45"/>
+      <c r="S55" s="45"/>
+      <c r="T55" s="46"/>
+      <c r="U55" s="46"/>
+      <c r="V55" s="46"/>
+      <c r="W55" s="46"/>
+      <c r="X55" s="47"/>
       <c r="Y55" s="4"/>
       <c r="Z55" s="5"/>
       <c r="AA55" s="5"/>
@@ -32674,30 +32703,30 @@
       <c r="AIF55" s="5"/>
     </row>
     <row r="56" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="35"/>
-      <c r="B56" s="35"/>
-      <c r="C56" s="40"/>
-      <c r="D56" s="40"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="37"/>
-      <c r="G56" s="37"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="41"/>
-      <c r="J56" s="41"/>
-      <c r="K56" s="23"/>
-      <c r="L56" s="51"/>
-      <c r="M56" s="51"/>
-      <c r="N56" s="51"/>
-      <c r="O56" s="51"/>
-      <c r="P56" s="56"/>
-      <c r="Q56" s="52"/>
-      <c r="R56" s="53"/>
-      <c r="S56" s="53"/>
-      <c r="T56" s="54"/>
-      <c r="U56" s="54"/>
-      <c r="V56" s="54"/>
-      <c r="W56" s="54"/>
-      <c r="X56" s="55"/>
+      <c r="A56" s="31"/>
+      <c r="B56" s="31"/>
+      <c r="C56" s="25"/>
+      <c r="D56" s="36"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="67"/>
+      <c r="G56" s="33"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="27"/>
+      <c r="J56" s="37"/>
+      <c r="K56" s="21"/>
+      <c r="L56" s="75"/>
+      <c r="M56" s="75"/>
+      <c r="N56" s="43"/>
+      <c r="O56" s="43"/>
+      <c r="P56" s="48"/>
+      <c r="Q56" s="44"/>
+      <c r="R56" s="45"/>
+      <c r="S56" s="45"/>
+      <c r="T56" s="46"/>
+      <c r="U56" s="46"/>
+      <c r="V56" s="46"/>
+      <c r="W56" s="46"/>
+      <c r="X56" s="47"/>
       <c r="Y56" s="4"/>
       <c r="Z56" s="5"/>
       <c r="AA56" s="5"/>
@@ -33592,108 +33621,108 @@
       <c r="AIF56" s="5"/>
     </row>
     <row r="57" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="35"/>
-      <c r="B57" s="35"/>
-      <c r="C57" s="36"/>
-      <c r="D57" s="36"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="37"/>
-      <c r="G57" s="37"/>
-      <c r="H57" s="20"/>
-      <c r="I57" s="38"/>
-      <c r="J57" s="38"/>
-      <c r="K57" s="23"/>
-      <c r="L57" s="51"/>
-      <c r="M57" s="51"/>
-      <c r="N57" s="51"/>
-      <c r="O57" s="51"/>
-      <c r="P57" s="56"/>
-      <c r="Q57" s="52"/>
-      <c r="R57" s="53"/>
-      <c r="S57" s="53"/>
-      <c r="T57" s="54"/>
-      <c r="U57" s="54"/>
-      <c r="V57" s="54"/>
-      <c r="W57" s="54"/>
-      <c r="X57" s="55"/>
+      <c r="A57" s="31"/>
+      <c r="B57" s="31"/>
+      <c r="C57" s="25"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="67"/>
+      <c r="G57" s="33"/>
+      <c r="H57" s="18"/>
+      <c r="I57" s="27"/>
+      <c r="J57" s="34"/>
+      <c r="K57" s="21"/>
+      <c r="L57" s="75"/>
+      <c r="M57" s="75"/>
+      <c r="N57" s="43"/>
+      <c r="O57" s="43"/>
+      <c r="P57" s="48"/>
+      <c r="Q57" s="44"/>
+      <c r="R57" s="45"/>
+      <c r="S57" s="45"/>
+      <c r="T57" s="46"/>
+      <c r="U57" s="46"/>
+      <c r="V57" s="46"/>
+      <c r="W57" s="46"/>
+      <c r="X57" s="47"/>
     </row>
     <row r="58" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="35"/>
-      <c r="B58" s="35"/>
-      <c r="C58" s="40"/>
-      <c r="D58" s="40"/>
-      <c r="E58" s="17"/>
-      <c r="F58" s="42"/>
-      <c r="G58" s="43"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="34"/>
-      <c r="J58" s="34"/>
-      <c r="K58" s="23"/>
-      <c r="L58" s="51"/>
-      <c r="M58" s="51"/>
-      <c r="N58" s="51"/>
-      <c r="O58" s="51"/>
-      <c r="P58" s="56"/>
-      <c r="Q58" s="52"/>
-      <c r="R58" s="53"/>
-      <c r="S58" s="53"/>
-      <c r="T58" s="54"/>
-      <c r="U58" s="54"/>
-      <c r="V58" s="54"/>
-      <c r="W58" s="54"/>
-      <c r="X58" s="55"/>
+      <c r="A58" s="31"/>
+      <c r="B58" s="31"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="36"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="68"/>
+      <c r="G58" s="38"/>
+      <c r="H58" s="18"/>
+      <c r="I58" s="71"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="21"/>
+      <c r="L58" s="75"/>
+      <c r="M58" s="75"/>
+      <c r="N58" s="43"/>
+      <c r="O58" s="43"/>
+      <c r="P58" s="48"/>
+      <c r="Q58" s="44"/>
+      <c r="R58" s="45"/>
+      <c r="S58" s="45"/>
+      <c r="T58" s="46"/>
+      <c r="U58" s="46"/>
+      <c r="V58" s="46"/>
+      <c r="W58" s="46"/>
+      <c r="X58" s="47"/>
     </row>
     <row r="59" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="35"/>
-      <c r="B59" s="35"/>
-      <c r="C59" s="36"/>
-      <c r="D59" s="36"/>
-      <c r="E59" s="17"/>
-      <c r="F59" s="37"/>
-      <c r="G59" s="37"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="38"/>
-      <c r="J59" s="38"/>
-      <c r="K59" s="23"/>
-      <c r="L59" s="51"/>
-      <c r="M59" s="51"/>
-      <c r="N59" s="51"/>
-      <c r="O59" s="51"/>
-      <c r="P59" s="56"/>
-      <c r="Q59" s="52"/>
-      <c r="R59" s="53"/>
-      <c r="S59" s="53"/>
-      <c r="T59" s="54"/>
-      <c r="U59" s="54"/>
-      <c r="V59" s="54"/>
-      <c r="W59" s="54"/>
-      <c r="X59" s="55"/>
+      <c r="A59" s="31"/>
+      <c r="B59" s="31"/>
+      <c r="C59" s="25"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="67"/>
+      <c r="G59" s="33"/>
+      <c r="H59" s="18"/>
+      <c r="I59" s="27"/>
+      <c r="J59" s="34"/>
+      <c r="K59" s="21"/>
+      <c r="L59" s="75"/>
+      <c r="M59" s="75"/>
+      <c r="N59" s="43"/>
+      <c r="O59" s="43"/>
+      <c r="P59" s="48"/>
+      <c r="Q59" s="44"/>
+      <c r="R59" s="45"/>
+      <c r="S59" s="45"/>
+      <c r="T59" s="46"/>
+      <c r="U59" s="46"/>
+      <c r="V59" s="46"/>
+      <c r="W59" s="46"/>
+      <c r="X59" s="47"/>
     </row>
     <row r="60" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="35"/>
-      <c r="B60" s="35"/>
-      <c r="C60" s="40"/>
-      <c r="D60" s="40"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="43"/>
-      <c r="G60" s="43"/>
-      <c r="H60" s="20"/>
-      <c r="I60" s="34"/>
-      <c r="J60" s="34"/>
-      <c r="K60" s="23"/>
-      <c r="L60" s="51"/>
-      <c r="M60" s="51"/>
-      <c r="N60" s="51"/>
-      <c r="O60" s="51"/>
-      <c r="P60" s="56"/>
-      <c r="Q60" s="52"/>
-      <c r="R60" s="53"/>
-      <c r="S60" s="53"/>
-      <c r="T60" s="54"/>
-      <c r="U60" s="54"/>
-      <c r="V60" s="54"/>
-      <c r="W60" s="54"/>
-      <c r="X60" s="55"/>
+      <c r="A60" s="31"/>
+      <c r="B60" s="31"/>
+      <c r="C60" s="25"/>
+      <c r="D60" s="36"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="69"/>
+      <c r="G60" s="38"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="71"/>
+      <c r="J60" s="30"/>
+      <c r="K60" s="21"/>
+      <c r="L60" s="75"/>
+      <c r="M60" s="75"/>
+      <c r="N60" s="43"/>
+      <c r="O60" s="43"/>
+      <c r="P60" s="48"/>
+      <c r="Q60" s="44"/>
+      <c r="R60" s="45"/>
+      <c r="S60" s="45"/>
+      <c r="T60" s="46"/>
+      <c r="U60" s="46"/>
+      <c r="V60" s="46"/>
+      <c r="W60" s="46"/>
+      <c r="X60" s="47"/>
       <c r="Y60" s="4"/>
       <c r="Z60" s="5"/>
       <c r="AA60" s="5"/>
@@ -34588,56 +34617,56 @@
       <c r="AIF60" s="5"/>
     </row>
     <row r="61" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="35"/>
-      <c r="B61" s="35"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="17"/>
-      <c r="F61" s="37"/>
-      <c r="G61" s="37"/>
-      <c r="H61" s="20"/>
-      <c r="I61" s="38"/>
-      <c r="J61" s="38"/>
-      <c r="K61" s="23"/>
-      <c r="L61" s="51"/>
-      <c r="M61" s="51"/>
-      <c r="N61" s="51"/>
-      <c r="O61" s="51"/>
-      <c r="P61" s="56"/>
-      <c r="Q61" s="52"/>
-      <c r="R61" s="53"/>
-      <c r="S61" s="53"/>
-      <c r="T61" s="54"/>
-      <c r="U61" s="54"/>
-      <c r="V61" s="54"/>
-      <c r="W61" s="54"/>
-      <c r="X61" s="55"/>
+      <c r="A61" s="31"/>
+      <c r="B61" s="31"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="32"/>
+      <c r="E61" s="16"/>
+      <c r="F61" s="67"/>
+      <c r="G61" s="33"/>
+      <c r="H61" s="18"/>
+      <c r="I61" s="27"/>
+      <c r="J61" s="34"/>
+      <c r="K61" s="21"/>
+      <c r="L61" s="75"/>
+      <c r="M61" s="75"/>
+      <c r="N61" s="43"/>
+      <c r="O61" s="43"/>
+      <c r="P61" s="48"/>
+      <c r="Q61" s="44"/>
+      <c r="R61" s="45"/>
+      <c r="S61" s="45"/>
+      <c r="T61" s="46"/>
+      <c r="U61" s="46"/>
+      <c r="V61" s="46"/>
+      <c r="W61" s="46"/>
+      <c r="X61" s="47"/>
     </row>
     <row r="62" spans="1:917" s="6" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="35"/>
-      <c r="B62" s="35"/>
-      <c r="C62" s="40"/>
-      <c r="D62" s="40"/>
-      <c r="E62" s="17"/>
-      <c r="F62" s="43"/>
-      <c r="G62" s="43"/>
-      <c r="H62" s="20"/>
-      <c r="I62" s="34"/>
-      <c r="J62" s="34"/>
-      <c r="K62" s="23"/>
-      <c r="L62" s="51"/>
-      <c r="M62" s="51"/>
-      <c r="N62" s="51"/>
-      <c r="O62" s="51"/>
-      <c r="P62" s="56"/>
-      <c r="Q62" s="52"/>
-      <c r="R62" s="53"/>
-      <c r="S62" s="53"/>
-      <c r="T62" s="54"/>
-      <c r="U62" s="54"/>
-      <c r="V62" s="54"/>
-      <c r="W62" s="54"/>
-      <c r="X62" s="55"/>
+      <c r="A62" s="31"/>
+      <c r="B62" s="31"/>
+      <c r="C62" s="25"/>
+      <c r="D62" s="36"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="69"/>
+      <c r="G62" s="38"/>
+      <c r="H62" s="18"/>
+      <c r="I62" s="71"/>
+      <c r="J62" s="30"/>
+      <c r="K62" s="21"/>
+      <c r="L62" s="75"/>
+      <c r="M62" s="75"/>
+      <c r="N62" s="43"/>
+      <c r="O62" s="43"/>
+      <c r="P62" s="48"/>
+      <c r="Q62" s="44"/>
+      <c r="R62" s="45"/>
+      <c r="S62" s="45"/>
+      <c r="T62" s="46"/>
+      <c r="U62" s="46"/>
+      <c r="V62" s="46"/>
+      <c r="W62" s="46"/>
+      <c r="X62" s="47"/>
       <c r="Y62" s="4"/>
       <c r="Z62" s="5"/>
       <c r="AA62" s="5"/>
@@ -35533,290 +35562,290 @@
       <c r="AIG62" s="3"/>
     </row>
     <row r="63" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="35"/>
-      <c r="B63" s="35"/>
-      <c r="C63" s="40"/>
-      <c r="D63" s="40"/>
-      <c r="E63" s="17"/>
-      <c r="F63" s="43"/>
-      <c r="G63" s="43"/>
-      <c r="H63" s="20"/>
-      <c r="I63" s="41"/>
-      <c r="J63" s="41"/>
-      <c r="K63" s="23"/>
-      <c r="L63" s="51"/>
-      <c r="M63" s="51"/>
-      <c r="N63" s="51"/>
-      <c r="O63" s="51"/>
-      <c r="P63" s="56"/>
-      <c r="Q63" s="52"/>
-      <c r="R63" s="53"/>
-      <c r="S63" s="53"/>
-      <c r="T63" s="54"/>
-      <c r="U63" s="54"/>
-      <c r="V63" s="54"/>
-      <c r="W63" s="54"/>
-      <c r="X63" s="55"/>
+      <c r="A63" s="31"/>
+      <c r="B63" s="31"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="36"/>
+      <c r="E63" s="16"/>
+      <c r="F63" s="69"/>
+      <c r="G63" s="38"/>
+      <c r="H63" s="18"/>
+      <c r="I63" s="27"/>
+      <c r="J63" s="37"/>
+      <c r="K63" s="21"/>
+      <c r="L63" s="75"/>
+      <c r="M63" s="75"/>
+      <c r="N63" s="43"/>
+      <c r="O63" s="43"/>
+      <c r="P63" s="48"/>
+      <c r="Q63" s="44"/>
+      <c r="R63" s="45"/>
+      <c r="S63" s="45"/>
+      <c r="T63" s="46"/>
+      <c r="U63" s="46"/>
+      <c r="V63" s="46"/>
+      <c r="W63" s="46"/>
+      <c r="X63" s="47"/>
     </row>
     <row r="64" spans="1:917" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="35"/>
-      <c r="B64" s="35"/>
-      <c r="C64" s="36"/>
-      <c r="D64" s="36"/>
-      <c r="E64" s="17"/>
-      <c r="F64" s="37"/>
-      <c r="G64" s="37"/>
-      <c r="H64" s="20"/>
-      <c r="I64" s="38"/>
-      <c r="J64" s="38"/>
-      <c r="K64" s="23"/>
-      <c r="L64" s="51"/>
-      <c r="M64" s="51"/>
-      <c r="N64" s="51"/>
-      <c r="O64" s="51"/>
-      <c r="P64" s="56"/>
-      <c r="Q64" s="52"/>
-      <c r="R64" s="53"/>
-      <c r="S64" s="53"/>
-      <c r="T64" s="54"/>
-      <c r="U64" s="54"/>
-      <c r="V64" s="54"/>
-      <c r="W64" s="54"/>
-      <c r="X64" s="55"/>
+      <c r="A64" s="31"/>
+      <c r="B64" s="31"/>
+      <c r="C64" s="25"/>
+      <c r="D64" s="32"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="67"/>
+      <c r="G64" s="33"/>
+      <c r="H64" s="18"/>
+      <c r="I64" s="27"/>
+      <c r="J64" s="34"/>
+      <c r="K64" s="21"/>
+      <c r="L64" s="75"/>
+      <c r="M64" s="75"/>
+      <c r="N64" s="43"/>
+      <c r="O64" s="43"/>
+      <c r="P64" s="48"/>
+      <c r="Q64" s="44"/>
+      <c r="R64" s="45"/>
+      <c r="S64" s="45"/>
+      <c r="T64" s="46"/>
+      <c r="U64" s="46"/>
+      <c r="V64" s="46"/>
+      <c r="W64" s="46"/>
+      <c r="X64" s="47"/>
     </row>
     <row r="65" spans="1:24" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="35"/>
-      <c r="B65" s="35"/>
-      <c r="C65" s="40"/>
-      <c r="D65" s="40"/>
-      <c r="E65" s="17"/>
-      <c r="F65" s="43"/>
-      <c r="G65" s="43"/>
-      <c r="H65" s="20"/>
-      <c r="I65" s="34"/>
-      <c r="J65" s="34"/>
-      <c r="K65" s="23"/>
-      <c r="L65" s="51"/>
-      <c r="M65" s="51"/>
-      <c r="N65" s="51"/>
-      <c r="O65" s="51"/>
-      <c r="P65" s="56"/>
-      <c r="Q65" s="52"/>
-      <c r="R65" s="53"/>
-      <c r="S65" s="53"/>
-      <c r="T65" s="54"/>
-      <c r="U65" s="54"/>
-      <c r="V65" s="54"/>
-      <c r="W65" s="54"/>
-      <c r="X65" s="55"/>
+      <c r="A65" s="31"/>
+      <c r="B65" s="31"/>
+      <c r="C65" s="25"/>
+      <c r="D65" s="36"/>
+      <c r="E65" s="16"/>
+      <c r="F65" s="69"/>
+      <c r="G65" s="38"/>
+      <c r="H65" s="18"/>
+      <c r="I65" s="71"/>
+      <c r="J65" s="30"/>
+      <c r="K65" s="21"/>
+      <c r="L65" s="75"/>
+      <c r="M65" s="75"/>
+      <c r="N65" s="43"/>
+      <c r="O65" s="43"/>
+      <c r="P65" s="48"/>
+      <c r="Q65" s="44"/>
+      <c r="R65" s="45"/>
+      <c r="S65" s="45"/>
+      <c r="T65" s="46"/>
+      <c r="U65" s="46"/>
+      <c r="V65" s="46"/>
+      <c r="W65" s="46"/>
+      <c r="X65" s="47"/>
     </row>
     <row r="66" spans="1:24" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="35"/>
-      <c r="B66" s="35"/>
-      <c r="C66" s="40"/>
-      <c r="D66" s="40"/>
-      <c r="E66" s="17"/>
-      <c r="F66" s="43"/>
-      <c r="G66" s="43"/>
-      <c r="H66" s="20"/>
-      <c r="I66" s="41"/>
-      <c r="J66" s="41"/>
-      <c r="K66" s="23"/>
-      <c r="L66" s="51"/>
-      <c r="M66" s="51"/>
-      <c r="N66" s="51"/>
-      <c r="O66" s="51"/>
-      <c r="P66" s="56"/>
-      <c r="Q66" s="52"/>
-      <c r="R66" s="53"/>
-      <c r="S66" s="53"/>
-      <c r="T66" s="54"/>
-      <c r="U66" s="54"/>
-      <c r="V66" s="54"/>
-      <c r="W66" s="54"/>
-      <c r="X66" s="55"/>
+      <c r="A66" s="31"/>
+      <c r="B66" s="31"/>
+      <c r="C66" s="25"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="16"/>
+      <c r="F66" s="69"/>
+      <c r="G66" s="38"/>
+      <c r="H66" s="18"/>
+      <c r="I66" s="27"/>
+      <c r="J66" s="37"/>
+      <c r="K66" s="21"/>
+      <c r="L66" s="75"/>
+      <c r="M66" s="75"/>
+      <c r="N66" s="43"/>
+      <c r="O66" s="43"/>
+      <c r="P66" s="48"/>
+      <c r="Q66" s="44"/>
+      <c r="R66" s="45"/>
+      <c r="S66" s="45"/>
+      <c r="T66" s="46"/>
+      <c r="U66" s="46"/>
+      <c r="V66" s="46"/>
+      <c r="W66" s="46"/>
+      <c r="X66" s="47"/>
     </row>
     <row r="67" spans="1:24" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="44"/>
-      <c r="B67" s="45"/>
-      <c r="C67" s="17"/>
-      <c r="D67" s="17"/>
-      <c r="E67" s="17"/>
-      <c r="F67" s="46"/>
-      <c r="G67" s="20"/>
-      <c r="H67" s="20"/>
-      <c r="I67" s="23"/>
-      <c r="J67" s="23"/>
-      <c r="K67" s="23"/>
-      <c r="L67" s="51"/>
-      <c r="M67" s="51"/>
-      <c r="N67" s="51"/>
-      <c r="O67" s="51"/>
-      <c r="P67" s="56"/>
-      <c r="Q67" s="52"/>
-      <c r="R67" s="53"/>
-      <c r="S67" s="53"/>
-      <c r="T67" s="54"/>
-      <c r="U67" s="54"/>
-      <c r="V67" s="54"/>
-      <c r="W67" s="54"/>
-      <c r="X67" s="55"/>
+      <c r="A67" s="39"/>
+      <c r="B67" s="40"/>
+      <c r="C67" s="62"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="66"/>
+      <c r="G67" s="18"/>
+      <c r="H67" s="18"/>
+      <c r="I67" s="72"/>
+      <c r="J67" s="21"/>
+      <c r="K67" s="21"/>
+      <c r="L67" s="75"/>
+      <c r="M67" s="75"/>
+      <c r="N67" s="43"/>
+      <c r="O67" s="43"/>
+      <c r="P67" s="48"/>
+      <c r="Q67" s="44"/>
+      <c r="R67" s="45"/>
+      <c r="S67" s="45"/>
+      <c r="T67" s="46"/>
+      <c r="U67" s="46"/>
+      <c r="V67" s="46"/>
+      <c r="W67" s="46"/>
+      <c r="X67" s="47"/>
     </row>
     <row r="68" spans="1:24" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="47"/>
-      <c r="B68" s="45"/>
-      <c r="C68" s="17"/>
-      <c r="D68" s="17"/>
-      <c r="E68" s="17"/>
-      <c r="F68" s="20"/>
-      <c r="G68" s="20"/>
-      <c r="H68" s="20"/>
-      <c r="I68" s="23"/>
-      <c r="J68" s="23"/>
-      <c r="K68" s="23"/>
-      <c r="L68" s="51"/>
-      <c r="M68" s="51"/>
-      <c r="N68" s="51"/>
-      <c r="O68" s="51"/>
-      <c r="P68" s="56"/>
-      <c r="Q68" s="52"/>
-      <c r="R68" s="53"/>
-      <c r="S68" s="53"/>
-      <c r="T68" s="54"/>
-      <c r="U68" s="54"/>
-      <c r="V68" s="54"/>
-      <c r="W68" s="54"/>
-      <c r="X68" s="55"/>
+      <c r="A68" s="41"/>
+      <c r="B68" s="40"/>
+      <c r="C68" s="62"/>
+      <c r="D68" s="16"/>
+      <c r="E68" s="16"/>
+      <c r="F68" s="66"/>
+      <c r="G68" s="18"/>
+      <c r="H68" s="18"/>
+      <c r="I68" s="72"/>
+      <c r="J68" s="21"/>
+      <c r="K68" s="21"/>
+      <c r="L68" s="75"/>
+      <c r="M68" s="75"/>
+      <c r="N68" s="43"/>
+      <c r="O68" s="43"/>
+      <c r="P68" s="48"/>
+      <c r="Q68" s="44"/>
+      <c r="R68" s="45"/>
+      <c r="S68" s="45"/>
+      <c r="T68" s="46"/>
+      <c r="U68" s="46"/>
+      <c r="V68" s="46"/>
+      <c r="W68" s="46"/>
+      <c r="X68" s="47"/>
     </row>
     <row r="69" spans="1:24" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="47"/>
-      <c r="B69" s="47"/>
-      <c r="C69" s="17"/>
-      <c r="D69" s="17"/>
-      <c r="E69" s="17"/>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
-      <c r="H69" s="20"/>
-      <c r="I69" s="23"/>
-      <c r="J69" s="23"/>
-      <c r="K69" s="23"/>
-      <c r="L69" s="51"/>
-      <c r="M69" s="51"/>
-      <c r="N69" s="51"/>
-      <c r="O69" s="51"/>
-      <c r="P69" s="56"/>
-      <c r="Q69" s="52"/>
-      <c r="R69" s="53"/>
-      <c r="S69" s="53"/>
-      <c r="T69" s="54"/>
-      <c r="U69" s="54"/>
-      <c r="V69" s="54"/>
-      <c r="W69" s="54"/>
-      <c r="X69" s="55"/>
+      <c r="A69" s="41"/>
+      <c r="B69" s="41"/>
+      <c r="C69" s="62"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="66"/>
+      <c r="G69" s="18"/>
+      <c r="H69" s="18"/>
+      <c r="I69" s="72"/>
+      <c r="J69" s="21"/>
+      <c r="K69" s="21"/>
+      <c r="L69" s="75"/>
+      <c r="M69" s="75"/>
+      <c r="N69" s="43"/>
+      <c r="O69" s="43"/>
+      <c r="P69" s="48"/>
+      <c r="Q69" s="44"/>
+      <c r="R69" s="45"/>
+      <c r="S69" s="45"/>
+      <c r="T69" s="46"/>
+      <c r="U69" s="46"/>
+      <c r="V69" s="46"/>
+      <c r="W69" s="46"/>
+      <c r="X69" s="47"/>
     </row>
     <row r="70" spans="1:24" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="48"/>
-      <c r="B70" s="48"/>
-      <c r="C70" s="17"/>
-      <c r="D70" s="17"/>
-      <c r="E70" s="17"/>
-      <c r="F70" s="46"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20"/>
-      <c r="I70" s="49"/>
-      <c r="J70" s="23"/>
-      <c r="K70" s="23"/>
-      <c r="L70" s="51"/>
-      <c r="M70" s="51"/>
-      <c r="N70" s="51"/>
-      <c r="O70" s="51"/>
-      <c r="P70" s="56"/>
-      <c r="Q70" s="52"/>
-      <c r="R70" s="53"/>
-      <c r="S70" s="53"/>
-      <c r="T70" s="54"/>
-      <c r="U70" s="54"/>
-      <c r="V70" s="54"/>
-      <c r="W70" s="54"/>
-      <c r="X70" s="55"/>
+      <c r="A70" s="42"/>
+      <c r="B70" s="42"/>
+      <c r="C70" s="62"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="66"/>
+      <c r="G70" s="18"/>
+      <c r="H70" s="18"/>
+      <c r="I70" s="72"/>
+      <c r="J70" s="21"/>
+      <c r="K70" s="21"/>
+      <c r="L70" s="75"/>
+      <c r="M70" s="75"/>
+      <c r="N70" s="43"/>
+      <c r="O70" s="43"/>
+      <c r="P70" s="48"/>
+      <c r="Q70" s="44"/>
+      <c r="R70" s="45"/>
+      <c r="S70" s="45"/>
+      <c r="T70" s="46"/>
+      <c r="U70" s="46"/>
+      <c r="V70" s="46"/>
+      <c r="W70" s="46"/>
+      <c r="X70" s="47"/>
     </row>
     <row r="71" spans="1:24" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="48"/>
-      <c r="B71" s="48"/>
-      <c r="C71" s="17"/>
-      <c r="D71" s="17"/>
-      <c r="E71" s="17"/>
-      <c r="F71" s="46"/>
-      <c r="G71" s="20"/>
-      <c r="H71" s="20"/>
-      <c r="I71" s="49"/>
-      <c r="J71" s="23"/>
-      <c r="K71" s="23"/>
-      <c r="L71" s="51"/>
-      <c r="M71" s="51"/>
-      <c r="N71" s="51"/>
-      <c r="O71" s="51"/>
-      <c r="P71" s="56"/>
-      <c r="Q71" s="52"/>
-      <c r="R71" s="53"/>
-      <c r="S71" s="53"/>
-      <c r="T71" s="54"/>
-      <c r="U71" s="54"/>
-      <c r="V71" s="54"/>
-      <c r="W71" s="54"/>
-      <c r="X71" s="55"/>
+      <c r="A71" s="42"/>
+      <c r="B71" s="42"/>
+      <c r="C71" s="62"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="66"/>
+      <c r="G71" s="18"/>
+      <c r="H71" s="18"/>
+      <c r="I71" s="72"/>
+      <c r="J71" s="21"/>
+      <c r="K71" s="21"/>
+      <c r="L71" s="75"/>
+      <c r="M71" s="75"/>
+      <c r="N71" s="43"/>
+      <c r="O71" s="43"/>
+      <c r="P71" s="48"/>
+      <c r="Q71" s="44"/>
+      <c r="R71" s="45"/>
+      <c r="S71" s="45"/>
+      <c r="T71" s="46"/>
+      <c r="U71" s="46"/>
+      <c r="V71" s="46"/>
+      <c r="W71" s="46"/>
+      <c r="X71" s="47"/>
     </row>
     <row r="72" spans="1:24" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="48"/>
-      <c r="B72" s="48"/>
-      <c r="C72" s="17"/>
-      <c r="D72" s="17"/>
-      <c r="E72" s="17"/>
-      <c r="F72" s="46"/>
-      <c r="G72" s="20"/>
-      <c r="H72" s="20"/>
-      <c r="I72" s="49"/>
-      <c r="J72" s="23"/>
-      <c r="K72" s="23"/>
-      <c r="L72" s="51"/>
-      <c r="M72" s="51"/>
-      <c r="N72" s="51"/>
-      <c r="O72" s="51"/>
-      <c r="P72" s="56"/>
-      <c r="Q72" s="52"/>
-      <c r="R72" s="53"/>
-      <c r="S72" s="53"/>
-      <c r="T72" s="54"/>
-      <c r="U72" s="54"/>
-      <c r="V72" s="54"/>
-      <c r="W72" s="54"/>
-      <c r="X72" s="55"/>
+      <c r="A72" s="42"/>
+      <c r="B72" s="42"/>
+      <c r="C72" s="62"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="16"/>
+      <c r="F72" s="66"/>
+      <c r="G72" s="18"/>
+      <c r="H72" s="18"/>
+      <c r="I72" s="72"/>
+      <c r="J72" s="21"/>
+      <c r="K72" s="21"/>
+      <c r="L72" s="75"/>
+      <c r="M72" s="75"/>
+      <c r="N72" s="43"/>
+      <c r="O72" s="43"/>
+      <c r="P72" s="48"/>
+      <c r="Q72" s="44"/>
+      <c r="R72" s="45"/>
+      <c r="S72" s="45"/>
+      <c r="T72" s="46"/>
+      <c r="U72" s="46"/>
+      <c r="V72" s="46"/>
+      <c r="W72" s="46"/>
+      <c r="X72" s="47"/>
     </row>
     <row r="73" spans="1:24" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="48"/>
-      <c r="B73" s="48"/>
-      <c r="C73" s="17"/>
-      <c r="D73" s="17"/>
-      <c r="E73" s="17"/>
-      <c r="F73" s="46"/>
-      <c r="G73" s="20"/>
-      <c r="H73" s="20"/>
-      <c r="I73" s="49"/>
-      <c r="J73" s="23"/>
-      <c r="K73" s="23"/>
-      <c r="L73" s="51"/>
-      <c r="M73" s="51"/>
-      <c r="N73" s="51"/>
-      <c r="O73" s="51"/>
-      <c r="P73" s="56"/>
-      <c r="Q73" s="52"/>
-      <c r="R73" s="53"/>
-      <c r="S73" s="53"/>
-      <c r="T73" s="54"/>
-      <c r="U73" s="54"/>
-      <c r="V73" s="54"/>
-      <c r="W73" s="54"/>
-      <c r="X73" s="55"/>
+      <c r="A73" s="42"/>
+      <c r="B73" s="42"/>
+      <c r="C73" s="62"/>
+      <c r="D73" s="16"/>
+      <c r="E73" s="16"/>
+      <c r="F73" s="66"/>
+      <c r="G73" s="18"/>
+      <c r="H73" s="18"/>
+      <c r="I73" s="72"/>
+      <c r="J73" s="21"/>
+      <c r="K73" s="21"/>
+      <c r="L73" s="75"/>
+      <c r="M73" s="75"/>
+      <c r="N73" s="43"/>
+      <c r="O73" s="43"/>
+      <c r="P73" s="48"/>
+      <c r="Q73" s="44"/>
+      <c r="R73" s="45"/>
+      <c r="S73" s="45"/>
+      <c r="T73" s="46"/>
+      <c r="U73" s="46"/>
+      <c r="V73" s="46"/>
+      <c r="W73" s="46"/>
+      <c r="X73" s="47"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:X59" xr:uid="{00000000-0009-0000-0000-000000000000}">
@@ -35829,6 +35858,6 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>